--- a/results/market_bookings_screen.xlsx
+++ b/results/market_bookings_screen.xlsx
@@ -4252,12 +4252,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>QSP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RESTAURANT BRANDS INTERNATIONAL INC.</t>
+          <t>RESTAURANT BRANDS INTERNATIONAL LIMITED PARTNERSHIP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4289,12 +4289,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>QSP</t>
+          <t>QSR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RESTAURANT BRANDS INTERNATIONAL LIMITED PARTNERSHIP</t>
+          <t>RESTAURANT BRANDS INTERNATIONAL INC.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10442,7 +10442,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>ZAYO GROUP LLC</t>
+          <t>ZAYO GROUP HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10474,7 +10474,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>ZAYO GROUP HOLDINGS, INC.</t>
+          <t>ZAYO GROUP LLC</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11145,67 +11145,72 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>NOBLE ENERGY INC</t>
+          <t>Moderna, Inc.</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2020Q2</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E299" s="3" t="n">
-        <v>7691</v>
+        <v>87.22499999999999</v>
       </c>
       <c r="F299" s="4" t="n">
-        <v>13.46935201401051</v>
+        <v>0.1527583187390543</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>4.061295971978984</v>
+        <v>0.9689667250437828</v>
       </c>
       <c r="H299" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>GBTG</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Moderna, Inc.</t>
+          <t>Global Business Travel Group, Inc.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>87.22499999999999</v>
+        <v>5</v>
       </c>
       <c r="F300" s="4" t="n">
-        <v>0.1527583187390543</v>
+        <v>0.008756567425569177</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>0.9689667250437828</v>
+        <v>0.9947460595446584</v>
       </c>
       <c r="H300" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -11214,39 +11219,34 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>GBTG</t>
-        </is>
-      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Global Business Travel Group, Inc.</t>
+          <t>NOBLE ENERGY INC</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="D301" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>5</v>
+        <v>7691</v>
       </c>
       <c r="F301" s="4" t="n">
-        <v>0.008756567425569177</v>
+        <v>13.46935201401051</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>0.9947460595446584</v>
+        <v>4.061295971978984</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
@@ -18533,7 +18533,7 @@
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>GCI, LLC</t>
+          <t>GRIZZLY MERGER SUB 1, LLC</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18565,7 +18565,7 @@
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>GRIZZLY MERGER SUB 1, LLC</t>
+          <t>GCI, LLC</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21148,71 +21148,71 @@
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>COHU</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>HOLLY ENERGY PARTNERS LP</t>
+          <t>COHU, INC.</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D588" s="3" t="n">
         <v>149.002</v>
       </c>
       <c r="E588" s="3" t="n">
-        <v>1557</v>
+        <v>4.8</v>
       </c>
       <c r="F588" s="4" t="n">
-        <v>10.44952416746084</v>
+        <v>0.03221433269352089</v>
       </c>
       <c r="G588" s="4" t="n">
-        <v>0.3892699426853331</v>
+        <v>0.999328868068885</v>
       </c>
       <c r="H588" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>COHU</t>
-        </is>
-      </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>COHU, INC.</t>
+          <t>HOLLY ENERGY PARTNERS LP</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2022Q3</t>
         </is>
       </c>
       <c r="D589" s="3" t="n">
         <v>149.002</v>
       </c>
       <c r="E589" s="3" t="n">
-        <v>4.8</v>
+        <v>1557</v>
       </c>
       <c r="F589" s="4" t="n">
-        <v>0.03221433269352089</v>
+        <v>10.44952416746084</v>
       </c>
       <c r="G589" s="4" t="n">
-        <v>0.999328868068885</v>
+        <v>0.3892699426853331</v>
       </c>
       <c r="H589" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
@@ -41152,187 +41152,187 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIF</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SIFCO Industries, Inc.</t>
+          <t>APOGEE ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Aircraft Engines &amp; Engine Parts</t>
+          <t>Glass Products, Made of  Purchased Glass</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1.24635685599541</v>
+        <v>1.250782977744257</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.2834245529574801</v>
+        <v>0.159544921305766</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2587123041888066</v>
+        <v>-0.1027090727833686</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.03814705786089556</v>
+        <v>0.01498367867502903</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>26.145</v>
+        <v>391.135</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>6.278829604130808</v>
+        <v>2.135485190535237</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>SIF</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ATI Inc.</t>
+          <t>SIFCO Industries, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Steel Pipe &amp; Tubes</t>
+          <t>Aircraft Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1.237887558480691</v>
+        <v>1.24635685599541</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.1233948448808717</v>
+        <v>-0.2834245529574801</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.1891891891891893</v>
+        <v>0.2587123041888066</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.1641891891891893</v>
+        <v>0.03814705786089556</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>1261.1</v>
+        <v>26.145</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3.489017524383475</v>
+        <v>6.278829604130808</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L3HARRIS TECHNOLOGIES, INC.</t>
+          <t>ATI Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Steel Pipe &amp; Tubes</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>1.221050841693589</v>
+        <v>1.237887558480691</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.01538664895575614</v>
+        <v>0.1233948448808717</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.1864406779661016</v>
+        <v>0.1891891891891893</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.03946293649172961</v>
+        <v>0.1641891891891893</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>5881</v>
+        <v>1261.1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>7.141642577792893</v>
+        <v>3.489017524383475</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CURTISS-WRIGHT CORPORATION</t>
+          <t>L3HARRIS TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1.216448342438594</v>
+        <v>1.221050841693589</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.06743040247502496</v>
+        <v>0.01538664895575614</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.1538461538461537</v>
+        <v>0.1864406779661016</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.008316008316008316</v>
+        <v>-0.03946293649172961</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>924.008</v>
+        <v>5881</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>4.870087704868356</v>
+        <v>7.141642577792893</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kaltura, Inc.</t>
+          <t>CURTISS-WRIGHT CORPORATION</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1.210176141937135</v>
+        <v>1.216448342438594</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.4663273037096317</v>
+        <v>0.06743040247502496</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.1264963534689886</v>
+        <v>0.1538461538461537</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.03789291408483597</v>
+        <v>-0.008316008316008316</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46.894</v>
+        <v>924.008</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>3.504222288565702</v>
+        <v>4.870087704868356</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Kaltura, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -41341,313 +41341,313 @@
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>1.206668788466228</v>
+        <v>1.210176141937135</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>-0.2868623654378923</v>
+        <v>0.4663273037096317</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>1.041666666666667</v>
+        <v>-0.1264963534689886</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.3267543859649122</v>
+        <v>0.03789291408483597</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>1935.464</v>
+        <v>46.894</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2.531692658711296</v>
+        <v>3.504222288565702</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LION</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lionsgate Studios Corp.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Services-Motion Picture &amp; Video Tape Production</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>1.201776976564512</v>
+        <v>1.206668788466228</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.1533162530604457</v>
+        <v>-0.2868623654378923</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1726737771239426</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.005564634360594845</v>
+        <v>-0.3267543859649122</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>776.6</v>
+        <v>1935.464</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2.463430337368014</v>
+        <v>2.531692658711296</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>LION</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IONQ, INC.</t>
+          <t>Lionsgate Studios Corp.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Services-Computer Integrated Systems Design</t>
+          <t>Services-Motion Picture &amp; Video Tape Production</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>1.18738288569644</v>
+        <v>1.201776976564512</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>-1.718096112687741</v>
+        <v>-0.1533162530604457</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>2.965658217497956</v>
+        <v>0.1726737771239426</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-2.571198527981877</v>
+        <v>-0.005564634360594845</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>80.05</v>
+        <v>776.6</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>6.058713304184884</v>
+        <v>2.463430337368014</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Zoom Communications, Inc.</t>
+          <t>IONQ, INC.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, Data Processing, Etc.</t>
+          <t>Services-Computer Integrated Systems Design</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>1.18579458306615</v>
+        <v>1.18738288569644</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>0.09921912048345316</v>
+        <v>-1.718096112687741</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.1407912275848193</v>
+        <v>2.965658217497956</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.03213314077183083</v>
+        <v>-2.571198527981877</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1277.217</v>
+        <v>80.05</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>3.551393381077764</v>
+        <v>6.058713304184884</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TELEDYNE TECHNOLOGIES INC</t>
+          <t>Zoom Communications, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Services-Computer Programming, Data Processing, Etc.</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>1.185684210526316</v>
+        <v>1.18579458306615</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>0.09706135300882623</v>
+        <v>0.09921912048345316</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.1624371182177506</v>
+        <v>0.1407912275848193</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.007519571652321755</v>
+        <v>0.03213314077183083</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>1662.5</v>
+        <v>1277.217</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3.113443609022557</v>
+        <v>3.551393381077764</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SYPRIS SOLUTIONS, INC.</t>
+          <t>TELEDYNE TECHNOLOGIES INC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Industrial Instruments For Measurement, Display, and Control</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>1.18483240499654</v>
+        <v>1.185684210526316</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.3969335313617212</v>
+        <v>0.09706135300882623</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.1565617433414043</v>
+        <v>0.1624371182177506</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.02008727213337846</v>
+        <v>0.007519571652321755</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>30.341</v>
+        <v>1662.5</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>2.296166902870703</v>
+        <v>3.113443609022557</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SYPR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QUALYS, INC.</t>
+          <t>SYPRIS SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Instruments For Measurement, Display, and Control</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>1.183746397694524</v>
+        <v>1.18483240499654</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>0.1201419674965454</v>
+        <v>0.3969335313617212</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.1538766927567208</v>
+        <v>-0.1565617433414043</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.06307113811062126</v>
+        <v>0.02008727213337846</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>182.175</v>
+        <v>30.341</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2.744114175929738</v>
+        <v>2.296166902870703</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ATRO</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ASTRONICS CORPORATION</t>
+          <t>QUALYS, INC.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aircraft Parts &amp; Auxiliary Equipment, NEC</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>1.178106379131934</v>
+        <v>1.183746397694524</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0.05102262668383295</v>
+        <v>0.1201419674965454</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.2094824914781532</v>
+        <v>0.1538766927567208</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.118397796084394</v>
+        <v>0.06307113811062126</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>259.957</v>
+        <v>182.175</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>3.002804309943568</v>
+        <v>2.744114175929738</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ATRO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Okta, Inc.</t>
+          <t>ASTRONICS CORPORATION</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Aircraft Parts &amp; Auxiliary Equipment, NEC</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1.172670807453416</v>
+        <v>1.178106379131934</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>-0.07750423045404342</v>
+        <v>0.05102262668383295</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.1700385356454721</v>
+        <v>0.2094824914781532</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.01455371684037909</v>
+        <v>0.118397796084394</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>805</v>
+        <v>259.957</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>6.034782608695652</v>
+        <v>3.002804309943568</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketWise, Inc.</t>
+          <t>Okta, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -41656,547 +41656,547 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>1.172396053186999</v>
+        <v>1.172670807453416</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>0.2518506078616183</v>
+        <v>-0.07750423045404342</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.0169517371082929</v>
+        <v>0.1700385356454721</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.08271509257012433</v>
+        <v>0.01455371684037909</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>75.80800000000001</v>
+        <v>805</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>5.102363866610384</v>
+        <v>6.034782608695652</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TETRA TECH, INC.</t>
+          <t>MarketWise, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Services-Engineering Services</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1.16432782725984</v>
+        <v>1.172396053186999</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>0.1656832287510965</v>
+        <v>0.2518506078616183</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.04717541414962878</v>
+        <v>-0.0169517371082929</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.05611913504811084</v>
+        <v>0.08271509257012433</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>1308.555</v>
+        <v>75.80800000000001</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3.392891395470576</v>
+        <v>5.102363866610384</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KTOS</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KRATOS DEFENSE &amp; SECURITY SOLUTIONS, INC.</t>
+          <t>TETRA TECH, INC.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Guided Missiles &amp; Space Vehicles &amp; Parts</t>
+          <t>Services-Engineering Services</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1.159110723626853</v>
+        <v>1.16432782725984</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.3879510030450943</v>
+        <v>0.1656832287510965</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.4742501414827391</v>
+        <v>0.04717541414962878</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.1407841909489549</v>
+        <v>0.05611913504811084</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>458.8</v>
+        <v>1308.555</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>4.542284219703574</v>
+        <v>3.392891395470576</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>KTOS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MERCURY SYSTEMS, INC.</t>
+          <t>KRATOS DEFENSE &amp; SECURITY SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Electronic Components &amp; Accessories</t>
+          <t>Guided Missiles &amp; Space Vehicles &amp; Parts</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1.153720536649714</v>
+        <v>1.159110723626853</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>0.1772017080099503</v>
+        <v>-0.3879510030450943</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.1891996564206053</v>
+        <v>0.4742501414827391</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.1197045453118029</v>
+        <v>0.1407841909489549</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>235.759</v>
+        <v>458.8</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3.646791851000386</v>
+        <v>4.542284219703574</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PARKER-HANNIFIN CORPORATION</t>
+          <t>MERCURY SYSTEMS, INC.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miscellaneous Fabricated Metal Products</t>
+          <t>Electronic Components &amp; Accessories</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1.1458257382428</v>
+        <v>1.153720536649714</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>0.0667841611548341</v>
+        <v>0.1772017080099503</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1363636363636365</v>
+        <v>0.1891996564206053</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.02207792207792214</v>
+        <v>0.1197045453118029</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>5486</v>
+        <v>235.759</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>2.278527160043748</v>
+        <v>3.646791851000386</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton Holding Corporation</t>
+          <t>PARKER-HANNIFIN CORPORATION</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Services-Management Consulting Services</t>
+          <t>Miscellaneous Fabricated Metal Products</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>1.142857142857143</v>
+        <v>1.1458257382428</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>0.04801010639320102</v>
+        <v>0.0667841611548341</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.04716981132075482</v>
+        <v>0.1363636363636365</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.07914597815292934</v>
+        <v>0.02207792207792214</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>2800</v>
+        <v>5486</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>3.964285714285714</v>
+        <v>2.278527160043748</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FORTINET, INC.</t>
+          <t>Booz Allen Hamilton Holding Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Computer Peripheral Equipment, NEC</t>
+          <t>Services-Management Consulting Services</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>1.136725426046194</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.007883515681929465</v>
+        <v>0.04801010639320102</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.1641566265060241</v>
+        <v>0.04716981132075482</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.01623674977258815</v>
+        <v>-0.07914597815292934</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>2047.9</v>
+        <v>2800</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>3.774598369060989</v>
+        <v>3.964285714285714</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AvePoint, Inc.</t>
+          <t>FORTINET, INC.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Computer Peripheral Equipment, NEC</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>1.135748423631471</v>
+        <v>1.136725426046194</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>-0.1029409980011255</v>
+        <v>-0.007883515681929465</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.2152943732348467</v>
+        <v>0.1641566265060241</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.1238811389843584</v>
+        <v>0.01623674977258815</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>124.495</v>
+        <v>2047.9</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>4.493353146712719</v>
+        <v>3.774598369060989</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>APG</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>APi Group Corporation</t>
+          <t>AvePoint, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Services-To Dwellings &amp; Other Buildings</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1.130434782608696</v>
+        <v>1.135748423631471</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>0.1348292934896971</v>
+        <v>-0.1029409980011255</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.06775210084033612</v>
+        <v>0.2152943732348467</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.1022230852638824</v>
+        <v>-0.1238811389843584</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>2254</v>
+        <v>124.495</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1.803904170363798</v>
+        <v>4.493353146712719</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>APG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CRANE COMPANY</t>
+          <t>APi Group Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miscellaneous Fabricated Metal Products</t>
+          <t>Services-To Dwellings &amp; Other Buildings</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>1.127639023044018</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>-0.03277732695389224</v>
+        <v>0.1348292934896971</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.2963115598598804</v>
+        <v>0.06775210084033612</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.03316992162160104</v>
+        <v>-0.1022230852638824</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>724.7</v>
+        <v>2254</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2.604250034497033</v>
+        <v>1.803904170363798</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APPIAN CORPORATION</t>
+          <t>CRANE COMPANY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Miscellaneous Fabricated Metal Products</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>1.12398157987956</v>
+        <v>1.127639023044018</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>0.04391895225970499</v>
+        <v>-0.03277732695389224</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1303326102675342</v>
+        <v>0.2963115598598804</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.02570668851882685</v>
+        <v>-0.03316992162160104</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>203.256</v>
+        <v>724.7</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>3.076415948360688</v>
+        <v>2.604250034497033</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
+          <t>APPIAN CORPORATION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Services-Computer Programming Services</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1.12114577631819</v>
+        <v>1.12398157987956</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>0.1092075518985325</v>
+        <v>0.04391895225970499</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.1409075961854653</v>
+        <v>0.1303326102675342</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.02574854162708617</v>
+        <v>-0.02570668851882685</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>5481</v>
+        <v>203.256</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>1.266009852216749</v>
+        <v>3.076415948360688</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JOHNSON CONTROLS INTERNATIONAL PLC</t>
+          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Air-Cond &amp; Warm Air Heatg Equip &amp; Comm &amp; Indl Refrig Equip</t>
+          <t>Services-Computer Programming Services</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1.120955548835803</v>
+        <v>1.12114577631819</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>-0.1022655963650549</v>
+        <v>0.1092075518985325</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.2098214285714286</v>
+        <v>0.1409075961854653</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.01436688311688306</v>
+        <v>0.02574854162708617</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>6614</v>
+        <v>5481</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4.097369216812822</v>
+        <v>1.266009852216749</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>STERIS plc</t>
+          <t>JOHNSON CONTROLS INTERNATIONAL PLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
+          <t>Air-Cond &amp; Warm Air Heatg Equip &amp; Comm &amp; Indl Refrig Equip</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>1.117371206538487</v>
+        <v>1.120955548835803</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>0.06231348307537887</v>
+        <v>-0.1022655963650549</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-0.1549342105263157</v>
+        <v>0.2098214285714286</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.02107338887658838</v>
+        <v>0.01436688311688306</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>1492.7</v>
+        <v>6614</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>1.032625443826623</v>
+        <v>4.097369216812822</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TARGET HOSPITALITY CORP.</t>
+          <t>STERIS plc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hotels, Rooming Houses, Camps &amp; Other Lodging Places</t>
+          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>1.116868527295068</v>
+        <v>1.117371206538487</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.3724613123743221</v>
+        <v>0.06231348307537887</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.7089351205738208</v>
+        <v>-0.1549342105263157</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.063535143960467</v>
+        <v>0.02107338887658838</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>85.455</v>
+        <v>1492.7</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>3.080802761687438</v>
+        <v>1.032625443826623</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>APOGEE ENTERPRISES, INC.</t>
+          <t>TARGET HOSPITALITY CORP.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Glass Products, Made of  Purchased Glass</t>
+          <t>Hotels, Rooming Houses, Camps &amp; Other Lodging Places</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>1.116652659593095</v>
+        <v>1.116868527295068</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>0.1032259540146929</v>
+        <v>-0.3724613123743221</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-0.1176927514583976</v>
+        <v>0.7089351205738208</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.08640549223298977</v>
+        <v>0.063535143960467</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>342.684</v>
+        <v>85.455</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>2.151174259667799</v>
+        <v>3.080802761687438</v>
       </c>
     </row>
     <row r="106">
@@ -44933,72 +44933,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATI Inc.</t>
+          <t>APOGEE ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Steel Pipe &amp; Tubes</t>
+          <t>Glass Products, Made of  Purchased Glass</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q3</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1261.1</v>
+        <v>391.135</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4400</v>
+        <v>835.263</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.489017524383475</v>
+        <v>2.135485190535237</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.237887558480691</v>
+        <v>1.250782977744257</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.145341424820038</v>
+        <v>1.086085316052114</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.11449271359982</v>
+        <v>1.091238056438491</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1233948448808717</v>
+        <v>0.159544921305766</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.1891891891891893</v>
+        <v>-0.1027090727833686</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.1641891891891893</v>
+        <v>0.01498367867502903</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.1058400561206592</v>
+        <v>0.09196413116914282</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>300</v>
+        <v>98.09000000000003</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L3HARRIS TECHNOLOGIES, INC.</t>
+          <t>ATI Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Steel Pipe &amp; Tubes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -45007,53 +45007,53 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5881</v>
+        <v>1261.1</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>42000</v>
+        <v>4400</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.141642577792893</v>
+        <v>3.489017524383475</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.221050841693589</v>
+        <v>1.237887558480691</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.209510854976772</v>
+        <v>1.145341424820038</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.205664192737833</v>
+        <v>1.11449271359982</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.01538664895575614</v>
+        <v>0.1233948448808717</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.1864406779661016</v>
+        <v>0.1891891891891893</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-0.03946293649172961</v>
+        <v>0.1641891891891893</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.08385551050497608</v>
+        <v>0.1058400561206592</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>1300</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CURTISS-WRIGHT CORPORATION</t>
+          <t>L3HARRIS TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -45062,53 +45062,53 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>924.008</v>
+        <v>5881</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4500</v>
+        <v>42000</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.870087704868356</v>
+        <v>7.141642577792893</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.216448342438594</v>
+        <v>1.221050841693589</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.145113894458274</v>
+        <v>1.209510854976772</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.149017939963569</v>
+        <v>1.205664192737833</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.06743040247502496</v>
+        <v>0.01538664895575614</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.1538461538461537</v>
+        <v>0.1864406779661016</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>-0.008316008316008316</v>
+        <v>-0.03946293649172961</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.0541105391888439</v>
+        <v>0.08385551050497608</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kaltura, Inc.</t>
+          <t>CURTISS-WRIGHT CORPORATION</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -45117,53 +45117,53 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46.894</v>
+        <v>924.008</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>164.327</v>
+        <v>4500</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.504222288565702</v>
+        <v>4.870087704868356</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.210176141937135</v>
+        <v>1.216448342438594</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.8604306641549109</v>
+        <v>1.145113894458274</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.7438488382275029</v>
+        <v>1.149017939963569</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.4663273037096317</v>
+        <v>0.06743040247502496</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.1264963534689886</v>
+        <v>0.1538461538461537</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.03789291408483597</v>
+        <v>-0.008316008316008316</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.05469839413431687</v>
+        <v>0.0541105391888439</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>9.855999999999995</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zoom Communications, Inc.</t>
+          <t>Kaltura, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, Data Processing, Etc.</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -45172,53 +45172,53 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1277.217</v>
+        <v>46.894</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4535.9</v>
+        <v>164.327</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>3.551393381077764</v>
+        <v>3.504222288565702</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.18579458306615</v>
+        <v>1.210176141937135</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.11138024270356</v>
+        <v>0.8604306641549109</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.086575462582697</v>
+        <v>0.7438488382275029</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.09921912048345316</v>
+        <v>0.4663273037096317</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.1407912275848193</v>
+        <v>-0.1264963534689886</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.03213314077183083</v>
+        <v>0.03789291408483597</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.04928415160031774</v>
+        <v>0.05469839413431687</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>237.2999999999993</v>
+        <v>9.855999999999995</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TELEDYNE TECHNOLOGIES INC</t>
+          <t>Zoom Communications, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Services-Computer Programming, Data Processing, Etc.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -45227,53 +45227,53 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1662.5</v>
+        <v>1277.217</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5176.1</v>
+        <v>4535.9</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>3.113443609022557</v>
+        <v>3.551393381077764</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.185684210526316</v>
+        <v>1.18579458306615</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1.112888195769697</v>
+        <v>1.11138024270356</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1.08862285751749</v>
+        <v>1.086575462582697</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.09706135300882623</v>
+        <v>0.09921912048345316</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.1624371182177506</v>
+        <v>0.1407912275848193</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.007519571652321755</v>
+        <v>0.03213314077183083</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.09830217348219583</v>
+        <v>0.04928415160031774</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>308.7000000000007</v>
+        <v>237.2999999999993</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SYPRIS SOLUTIONS, INC.</t>
+          <t>TELEDYNE TECHNOLOGIES INC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Industrial Instruments For Measurement, Display, and Control</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -45282,53 +45282,53 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>30.341</v>
+        <v>1662.5</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>69.66800000000001</v>
+        <v>5176.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2.296166902870703</v>
+        <v>3.113443609022557</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.18483240499654</v>
+        <v>1.185684210526316</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.8871322564752486</v>
+        <v>1.112888195769697</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>0.7878988736348184</v>
+        <v>1.08862285751749</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.3969335313617212</v>
+        <v>0.09706135300882623</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.1565617433414043</v>
+        <v>0.1624371182177506</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.02008727213337846</v>
+        <v>0.007519571652321755</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>-0.03452555209062547</v>
+        <v>0.09830217348219583</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>5.608000000000004</v>
+        <v>308.7000000000007</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SYPR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>QUALYS, INC.</t>
+          <t>SYPRIS SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Instruments For Measurement, Display, and Control</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -45337,48 +45337,48 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>182.175</v>
+        <v>30.341</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>499.909</v>
+        <v>69.66800000000001</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2.744114175929738</v>
+        <v>2.296166902870703</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.183746397694524</v>
+        <v>1.18483240499654</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1.093639922072115</v>
+        <v>0.8871322564752486</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1.063604430197979</v>
+        <v>0.7878988736348184</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.1201419674965454</v>
+        <v>0.3969335313617212</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.1538766927567208</v>
+        <v>-0.1565617433414043</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.06307113811062126</v>
+        <v>0.02008727213337846</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.110403384086504</v>
+        <v>-0.03452555209062547</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>33.47399999999999</v>
+        <v>5.608000000000004</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MarketWise, Inc.</t>
+          <t>QUALYS, INC.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -45392,53 +45392,53 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>75.80800000000001</v>
+        <v>182.175</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>386.8</v>
+        <v>499.909</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>5.102363866610384</v>
+        <v>2.744114175929738</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.172396053186999</v>
+        <v>1.183746397694524</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>0.9835080972907853</v>
+        <v>1.093639922072115</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.9205454453253807</v>
+        <v>1.063604430197979</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.2518506078616183</v>
+        <v>0.1201419674965454</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.0169517371082929</v>
+        <v>0.1538766927567208</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.08271509257012433</v>
+        <v>0.06307113811062126</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>-0.05180737961225756</v>
+        <v>0.110403384086504</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>13.06900000000002</v>
+        <v>33.47399999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TETRA TECH, INC.</t>
+          <t>MarketWise, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Services-Engineering Services</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -45447,108 +45447,108 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1308.555</v>
+        <v>75.80800000000001</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>4439.785</v>
+        <v>386.8</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>3.392891395470576</v>
+        <v>5.102363866610384</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.16432782725984</v>
+        <v>1.172396053186999</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1.040065405696518</v>
+        <v>0.9835080972907853</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.9986445985087435</v>
+        <v>0.9205454453253807</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.1656832287510965</v>
+        <v>0.2518506078616183</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.04717541414962878</v>
+        <v>-0.0169517371082929</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.05611913504811084</v>
+        <v>0.08271509257012433</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>-0.04472206486126606</v>
+        <v>-0.05180737961225756</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>215.0320000000002</v>
+        <v>13.06900000000002</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MERCURY SYSTEMS, INC.</t>
+          <t>TETRA TECH, INC.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Electronic Components &amp; Accessories</t>
+          <t>Services-Engineering Services</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>235.759</v>
+        <v>1308.555</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>859.764</v>
+        <v>4439.785</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>3.646791851000386</v>
+        <v>3.392891395470576</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.153720536649714</v>
+        <v>1.16432782725984</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1.101936469459621</v>
+        <v>1.040065405696518</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0.976518828639764</v>
+        <v>0.9986445985087435</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.1772017080099503</v>
+        <v>0.1656832287510965</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.1891996564206053</v>
+        <v>0.04717541414962878</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.1197045453118029</v>
+        <v>0.05611913504811084</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.1154486700290502</v>
+        <v>-0.04472206486126606</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>36.24099999999999</v>
+        <v>215.0320000000002</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PARKER-HANNIFIN CORPORATION</t>
+          <t>MERCURY SYSTEMS, INC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miscellaneous Fabricated Metal Products</t>
+          <t>Electronic Components &amp; Accessories</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -45557,108 +45557,108 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>5486</v>
+        <v>235.759</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>12500</v>
+        <v>859.764</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2.278527160043748</v>
+        <v>3.646791851000386</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.1458257382428</v>
+        <v>1.153720536649714</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1.094048005964598</v>
+        <v>1.101936469459621</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1.079041577087966</v>
+        <v>0.976518828639764</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.0667841611548341</v>
+        <v>0.1772017080099503</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.1363636363636365</v>
+        <v>0.1891996564206053</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.02207792207792214</v>
+        <v>0.1197045453118029</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.1060483870967741</v>
+        <v>0.1154486700290502</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>800</v>
+        <v>36.24099999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton Holding Corporation</t>
+          <t>PARKER-HANNIFIN CORPORATION</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Services-Management Consulting Services</t>
+          <t>Miscellaneous Fabricated Metal Products</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2800</v>
+        <v>5486</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>11100</v>
+        <v>12500</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>3.964285714285714</v>
+        <v>2.278527160043748</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.142857142857143</v>
+        <v>1.1458257382428</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1.017067087274964</v>
+        <v>1.094048005964598</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1.094847036463942</v>
+        <v>1.079041577087966</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.04801010639320102</v>
+        <v>0.0667841611548341</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.04716981132075482</v>
+        <v>0.1363636363636365</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>-0.07914597815292934</v>
+        <v>0.02207792207792214</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>-0.04240766073871405</v>
+        <v>0.1060483870967741</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APG</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>APi Group Corporation</t>
+          <t>Booz Allen Hamilton Holding Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Services-To Dwellings &amp; Other Buildings</t>
+          <t>Services-Management Consulting Services</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -45667,53 +45667,53 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2254</v>
+        <v>2800</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>4066</v>
+        <v>11100</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1.803904170363798</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.130434782608696</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1.029312812491423</v>
+        <v>1.017067087274964</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>0.9956054891189985</v>
+        <v>1.094847036463942</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.1348292934896971</v>
+        <v>0.04801010639320102</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.06775210084033612</v>
+        <v>0.04716981132075482</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-0.1022230852638824</v>
+        <v>-0.07914597815292934</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.1326633165829145</v>
+        <v>-0.04240766073871405</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>294</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>APG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
+          <t>APi Group Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Services-Computer Programming Services</t>
+          <t>Services-To Dwellings &amp; Other Buildings</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -45722,53 +45722,53 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>5481</v>
+        <v>2254</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>6939</v>
+        <v>4066</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1.266009852216749</v>
+        <v>1.803904170363798</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.12114577631819</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1.03924011239429</v>
+        <v>1.029312812491423</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1.011938224419658</v>
+        <v>0.9956054891189985</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.1092075518985325</v>
+        <v>0.1348292934896971</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.1409075961854653</v>
+        <v>0.06775210084033612</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.02574854162708617</v>
+        <v>-0.1022230852638824</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.04499523355576729</v>
+        <v>0.1326633165829145</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>664</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>STERIS plc</t>
+          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
+          <t>Services-Computer Programming Services</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -45777,53 +45777,53 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1492.7</v>
+        <v>5481</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1541.4</v>
+        <v>6939</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1.032625443826623</v>
+        <v>1.266009852216749</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.117371206538487</v>
+        <v>1.12114577631819</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1.054410773906568</v>
+        <v>1.03924011239429</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>1.055057723463108</v>
+        <v>1.011938224419658</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.06231348307537887</v>
+        <v>0.1092075518985325</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.1549342105263157</v>
+        <v>0.1409075961854653</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.02107338887658838</v>
+        <v>0.02574854162708617</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.07303572712242112</v>
+        <v>0.04499523355576729</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>175.2</v>
+        <v>664</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>APOGEE ENTERPRISES, INC.</t>
+          <t>STERIS plc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Glass Products, Made of  Purchased Glass</t>
+          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -45832,37 +45832,37 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>342.684</v>
+        <v>1492.7</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>737.173</v>
+        <v>1541.4</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>2.151174259667799</v>
+        <v>1.032625443826623</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.116652659593095</v>
+        <v>1.117371206538487</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1.091238056438491</v>
+        <v>1.054410773906568</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>1.013426705578402</v>
+        <v>1.055057723463108</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0.1032259540146929</v>
+        <v>0.06231348307537887</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.1176927514583976</v>
+        <v>-0.1549342105263157</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.08640549223298977</v>
+        <v>0.02107338887658838</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>-0.01136107921597584</v>
+        <v>0.07303572712242112</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>39.97500000000002</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="48">
@@ -61521,72 +61521,72 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIF</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SIFCO Industries, Inc.</t>
+          <t>APOGEE ENTERPRISES, INC.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Aircraft Engines &amp; Engine Parts</t>
+          <t>Glass Products, Made of  Purchased Glass</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q3</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>26.145</v>
+        <v>391.135</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>164.16</v>
+        <v>835.263</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>6.278829604130808</v>
+        <v>2.135485190535237</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.24635685599541</v>
+        <v>1.250782977744257</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1.593781631223669</v>
+        <v>1.086085316052114</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>1.52978140895289</v>
+        <v>1.091238056438491</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-0.2834245529574801</v>
+        <v>0.159544921305766</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.2587123041888066</v>
+        <v>-0.1027090727833686</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.03814705786089556</v>
+        <v>0.01498367867502903</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.1832993890020367</v>
+        <v>0.09196413116914282</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>6.441000000000003</v>
+        <v>98.09000000000003</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>SIF</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ATI Inc.</t>
+          <t>SIFCO Industries, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Steel Pipe &amp; Tubes</t>
+          <t>Aircraft Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -61595,53 +61595,53 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1261.1</v>
+        <v>26.145</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>4400</v>
+        <v>164.16</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>3.489017524383475</v>
+        <v>6.278829604130808</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1.237887558480691</v>
+        <v>1.24635685599541</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1.145341424820038</v>
+        <v>1.593781631223669</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>1.11449271359982</v>
+        <v>1.52978140895289</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0.1233948448808717</v>
+        <v>-0.2834245529574801</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.1891891891891893</v>
+        <v>0.2587123041888066</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.1641891891891893</v>
+        <v>0.03814705786089556</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.1058400561206592</v>
+        <v>0.1832993890020367</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>300</v>
+        <v>6.441000000000003</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L3HARRIS TECHNOLOGIES, INC.</t>
+          <t>ATI Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Steel Pipe &amp; Tubes</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -61650,53 +61650,53 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>5881</v>
+        <v>1261.1</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>42000</v>
+        <v>4400</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7.141642577792893</v>
+        <v>3.489017524383475</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.221050841693589</v>
+        <v>1.237887558480691</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1.209510854976772</v>
+        <v>1.145341424820038</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.205664192737833</v>
+        <v>1.11449271359982</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.01538664895575614</v>
+        <v>0.1233948448808717</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.1864406779661016</v>
+        <v>0.1891891891891893</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-0.03946293649172961</v>
+        <v>0.1641891891891893</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0.08385551050497608</v>
+        <v>0.1058400561206592</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>1300</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CURTISS-WRIGHT CORPORATION</t>
+          <t>L3HARRIS TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -61705,53 +61705,53 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>924.008</v>
+        <v>5881</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>4500</v>
+        <v>42000</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>4.870087704868356</v>
+        <v>7.141642577792893</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.216448342438594</v>
+        <v>1.221050841693589</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>1.145113894458274</v>
+        <v>1.209510854976772</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>1.149017939963569</v>
+        <v>1.205664192737833</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0.06743040247502496</v>
+        <v>0.01538664895575614</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.1538461538461537</v>
+        <v>0.1864406779661016</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>-0.008316008316008316</v>
+        <v>-0.03946293649172961</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.0541105391888439</v>
+        <v>0.08385551050497608</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kaltura, Inc.</t>
+          <t>CURTISS-WRIGHT CORPORATION</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Misc Industrial &amp; Commercial Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -61760,48 +61760,48 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46.894</v>
+        <v>924.008</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>164.327</v>
+        <v>4500</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>3.504222288565702</v>
+        <v>4.870087704868356</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.210176141937135</v>
+        <v>1.216448342438594</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0.8604306641549109</v>
+        <v>1.145113894458274</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>0.7438488382275029</v>
+        <v>1.149017939963569</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0.4663273037096317</v>
+        <v>0.06743040247502496</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.1264963534689886</v>
+        <v>0.1538461538461537</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.03789291408483597</v>
+        <v>-0.008316008316008316</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0.05469839413431687</v>
+        <v>0.0541105391888439</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>9.855999999999995</v>
+        <v>200</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Kaltura, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -61815,53 +61815,53 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1935.464</v>
+        <v>46.894</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>4900</v>
+        <v>164.327</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2.531692658711296</v>
+        <v>3.504222288565702</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.206668788466228</v>
+        <v>1.210176141937135</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>1.421815562544648</v>
+        <v>0.8604306641549109</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>1.493531153904121</v>
+        <v>0.7438488382275029</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-0.2868623654378923</v>
+        <v>0.4663273037096317</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>1.041666666666667</v>
+        <v>-0.1264963534689886</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-0.3267543859649122</v>
+        <v>0.03789291408483597</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.9283349457057259</v>
+        <v>0.05469839413431687</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>400</v>
+        <v>9.855999999999995</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LION</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lionsgate Studios Corp.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Services-Motion Picture &amp; Video Tape Production</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -61870,53 +61870,53 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>776.6</v>
+        <v>1935.464</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1913.1</v>
+        <v>4900</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2.463430337368014</v>
+        <v>2.531692658711296</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.201776976564512</v>
+        <v>1.206668788466228</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>1.333171769255608</v>
+        <v>1.421815562544648</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>1.355093229624957</v>
+        <v>1.493531153904121</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-0.1533162530604457</v>
+        <v>-0.2868623654378923</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.1726737771239426</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>-0.005564634360594845</v>
+        <v>-0.3267543859649122</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0.476706598212588</v>
+        <v>0.9283349457057259</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>156.6999999999998</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>LION</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IONQ, INC.</t>
+          <t>Lionsgate Studios Corp.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Services-Computer Integrated Systems Design</t>
+          <t>Services-Motion Picture &amp; Video Tape Production</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -61925,53 +61925,53 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>80.05</v>
+        <v>776.6</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>485</v>
+        <v>1913.1</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>6.058713304184884</v>
+        <v>2.463430337368014</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.18738288569644</v>
+        <v>1.201776976564512</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2.475954970212246</v>
+        <v>1.333171769255608</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>2.905478998384181</v>
+        <v>1.355093229624957</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-1.718096112687741</v>
+        <v>-0.1533162530604457</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>2.965658217497956</v>
+        <v>0.1726737771239426</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>-2.571198527981877</v>
+        <v>-0.005564634360594845</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>2.868270996424084</v>
+        <v>0.476706598212588</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>15</v>
+        <v>156.6999999999998</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Zoom Communications, Inc.</t>
+          <t>IONQ, INC.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, Data Processing, Etc.</t>
+          <t>Services-Computer Integrated Systems Design</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -61980,53 +61980,53 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1277.217</v>
+        <v>80.05</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>4535.9</v>
+        <v>485</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3.551393381077764</v>
+        <v>6.058713304184884</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.18579458306615</v>
+        <v>1.18738288569644</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>1.11138024270356</v>
+        <v>2.475954970212246</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>1.086575462582697</v>
+        <v>2.905478998384181</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0.09921912048345316</v>
+        <v>-1.718096112687741</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.1407912275848193</v>
+        <v>2.965658217497956</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.03213314077183083</v>
+        <v>-2.571198527981877</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.04928415160031774</v>
+        <v>2.868270996424084</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>237.2999999999993</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TELEDYNE TECHNOLOGIES INC</t>
+          <t>Zoom Communications, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
+          <t>Services-Computer Programming, Data Processing, Etc.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -62035,53 +62035,53 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1662.5</v>
+        <v>1277.217</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5176.1</v>
+        <v>4535.9</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3.113443609022557</v>
+        <v>3.551393381077764</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.185684210526316</v>
+        <v>1.18579458306615</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1.112888195769697</v>
+        <v>1.11138024270356</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>1.08862285751749</v>
+        <v>1.086575462582697</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0.09706135300882623</v>
+        <v>0.09921912048345316</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.1624371182177506</v>
+        <v>0.1407912275848193</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.007519571652321755</v>
+        <v>0.03213314077183083</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.09830217348219583</v>
+        <v>0.04928415160031774</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>308.7000000000007</v>
+        <v>237.2999999999993</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SYPRIS SOLUTIONS, INC.</t>
+          <t>TELEDYNE TECHNOLOGIES INC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Industrial Instruments For Measurement, Display, and Control</t>
+          <t>Search, Detection, Navigation, Guidance, Aeronautical Sys</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -62090,53 +62090,53 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>30.341</v>
+        <v>1662.5</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>69.66800000000001</v>
+        <v>5176.1</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2.296166902870703</v>
+        <v>3.113443609022557</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.18483240499654</v>
+        <v>1.185684210526316</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.8871322564752486</v>
+        <v>1.112888195769697</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>0.7878988736348184</v>
+        <v>1.08862285751749</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.3969335313617212</v>
+        <v>0.09706135300882623</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.1565617433414043</v>
+        <v>0.1624371182177506</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.02008727213337846</v>
+        <v>0.007519571652321755</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>-0.03452555209062547</v>
+        <v>0.09830217348219583</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>5.608000000000004</v>
+        <v>308.7000000000007</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SYPR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QUALYS, INC.</t>
+          <t>SYPRIS SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Instruments For Measurement, Display, and Control</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -62145,53 +62145,53 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>182.175</v>
+        <v>30.341</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>499.909</v>
+        <v>69.66800000000001</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>2.744114175929738</v>
+        <v>2.296166902870703</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.183746397694524</v>
+        <v>1.18483240499654</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1.093639922072115</v>
+        <v>0.8871322564752486</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1.063604430197979</v>
+        <v>0.7878988736348184</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0.1201419674965454</v>
+        <v>0.3969335313617212</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0.1538766927567208</v>
+        <v>-0.1565617433414043</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.06307113811062126</v>
+        <v>0.02008727213337846</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.110403384086504</v>
+        <v>-0.03452555209062547</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>33.47399999999999</v>
+        <v>5.608000000000004</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ATRO</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ASTRONICS CORPORATION</t>
+          <t>QUALYS, INC.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aircraft Parts &amp; Auxiliary Equipment, NEC</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -62200,53 +62200,53 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>259.957</v>
+        <v>182.175</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>780.6</v>
+        <v>499.909</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>3.002804309943568</v>
+        <v>2.744114175929738</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.178106379131934</v>
+        <v>1.183746397694524</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1.139839409119059</v>
+        <v>1.093639922072115</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>1.127083752448101</v>
+        <v>1.063604430197979</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0.05102262668383295</v>
+        <v>0.1201419674965454</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>0.2094824914781532</v>
+        <v>0.1538766927567208</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.118397796084394</v>
+        <v>0.06307113811062126</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.2700778784236704</v>
+        <v>0.110403384086504</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>46.30000000000007</v>
+        <v>33.47399999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ATRO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Okta, Inc.</t>
+          <t>ASTRONICS CORPORATION</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Aircraft Parts &amp; Auxiliary Equipment, NEC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -62255,48 +62255,48 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>805</v>
+        <v>259.957</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>4858</v>
+        <v>780.6</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>6.034782608695652</v>
+        <v>3.002804309943568</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.172670807453416</v>
+        <v>1.178106379131934</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1.230798980293949</v>
+        <v>1.139839409119059</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>1.25017503790746</v>
+        <v>1.127083752448101</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-0.07750423045404342</v>
+        <v>0.05102262668383295</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.1700385356454721</v>
+        <v>0.2094824914781532</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0.01455371684037909</v>
+        <v>0.118397796084394</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.1057692307692308</v>
+        <v>0.2700778784236704</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>139</v>
+        <v>46.30000000000007</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MarketWise, Inc.</t>
+          <t>Okta, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -62310,53 +62310,53 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>75.80800000000001</v>
+        <v>805</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>386.8</v>
+        <v>4858</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>5.102363866610384</v>
+        <v>6.034782608695652</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.172396053186999</v>
+        <v>1.172670807453416</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>0.9835080972907853</v>
+        <v>1.230798980293949</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>0.9205454453253807</v>
+        <v>1.25017503790746</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0.2518506078616183</v>
+        <v>-0.07750423045404342</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.0169517371082929</v>
+        <v>0.1700385356454721</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.08271509257012433</v>
+        <v>0.01455371684037909</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>-0.05180737961225756</v>
+        <v>0.1057692307692308</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>13.06900000000002</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TETRA TECH, INC.</t>
+          <t>MarketWise, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Services-Engineering Services</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -62365,53 +62365,53 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>1308.555</v>
+        <v>75.80800000000001</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4439.785</v>
+        <v>386.8</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3.392891395470576</v>
+        <v>5.102363866610384</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1.16432782725984</v>
+        <v>1.172396053186999</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>1.040065405696518</v>
+        <v>0.9835080972907853</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>0.9986445985087435</v>
+        <v>0.9205454453253807</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0.1656832287510965</v>
+        <v>0.2518506078616183</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.04717541414962878</v>
+        <v>-0.0169517371082929</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.05611913504811084</v>
+        <v>0.08271509257012433</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>-0.04472206486126606</v>
+        <v>-0.05180737961225756</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>215.0320000000002</v>
+        <v>13.06900000000002</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KTOS</t>
+          <t>TTEK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KRATOS DEFENSE &amp; SECURITY SOLUTIONS, INC.</t>
+          <t>TETRA TECH, INC.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Guided Missiles &amp; Space Vehicles &amp; Parts</t>
+          <t>Services-Engineering Services</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -62420,108 +62420,108 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>458.8</v>
+        <v>1308.555</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2084</v>
+        <v>4439.785</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>4.542284219703574</v>
+        <v>3.392891395470576</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.159110723626853</v>
+        <v>1.16432782725984</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>1.450073975910673</v>
+        <v>1.040065405696518</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>1.547061726671947</v>
+        <v>0.9986445985087435</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-0.3879510030450943</v>
+        <v>0.1656832287510965</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0.4742501414827391</v>
+        <v>0.04717541414962878</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.1407841909489549</v>
+        <v>0.05611913504811084</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0.3052631578947369</v>
+        <v>-0.04472206486126606</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>73</v>
+        <v>215.0320000000002</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MRCY</t>
+          <t>KTOS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MERCURY SYSTEMS, INC.</t>
+          <t>KRATOS DEFENSE &amp; SECURITY SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Electronic Components &amp; Accessories</t>
+          <t>Guided Missiles &amp; Space Vehicles &amp; Parts</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>235.759</v>
+        <v>458.8</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>859.764</v>
+        <v>2084</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>3.646791851000386</v>
+        <v>4.542284219703574</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>1.153720536649714</v>
+        <v>1.159110723626853</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1.101936469459621</v>
+        <v>1.450073975910673</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>0.976518828639764</v>
+        <v>1.547061726671947</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0.1772017080099503</v>
+        <v>-0.3879510030450943</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.1891996564206053</v>
+        <v>0.4742501414827391</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0.1197045453118029</v>
+        <v>0.1407841909489549</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.1154486700290502</v>
+        <v>0.3052631578947369</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>36.24099999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>MRCY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PARKER-HANNIFIN CORPORATION</t>
+          <t>MERCURY SYSTEMS, INC.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miscellaneous Fabricated Metal Products</t>
+          <t>Electronic Components &amp; Accessories</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -62530,108 +62530,108 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>5486</v>
+        <v>235.759</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>12500</v>
+        <v>859.764</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2.278527160043748</v>
+        <v>3.646791851000386</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1.1458257382428</v>
+        <v>1.153720536649714</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>1.094048005964598</v>
+        <v>1.101936469459621</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>1.079041577087966</v>
+        <v>0.976518828639764</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.0667841611548341</v>
+        <v>0.1772017080099503</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0.1363636363636365</v>
+        <v>0.1891996564206053</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.02207792207792214</v>
+        <v>0.1197045453118029</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0.1060483870967741</v>
+        <v>0.1154486700290502</v>
       </c>
       <c r="O94" s="3" t="n">
-        <v>800</v>
+        <v>36.24099999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton Holding Corporation</t>
+          <t>PARKER-HANNIFIN CORPORATION</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Services-Management Consulting Services</t>
+          <t>Miscellaneous Fabricated Metal Products</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>2800</v>
+        <v>5486</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>11100</v>
+        <v>12500</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3.964285714285714</v>
+        <v>2.278527160043748</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>1.142857142857143</v>
+        <v>1.1458257382428</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>1.017067087274964</v>
+        <v>1.094048005964598</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>1.094847036463942</v>
+        <v>1.079041577087966</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0.04801010639320102</v>
+        <v>0.0667841611548341</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0.04716981132075482</v>
+        <v>0.1363636363636365</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>-0.07914597815292934</v>
+        <v>0.02207792207792214</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.04240766073871405</v>
+        <v>0.1060483870967741</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FORTINET, INC.</t>
+          <t>Booz Allen Hamilton Holding Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Computer Peripheral Equipment, NEC</t>
+          <t>Services-Management Consulting Services</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -62640,53 +62640,53 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>2047.9</v>
+        <v>2800</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>7730</v>
+        <v>11100</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>3.774598369060989</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1.136725426046194</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1.142638062807641</v>
+        <v>1.017067087274964</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>1.144608941728123</v>
+        <v>1.094847036463942</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-0.007883515681929465</v>
+        <v>0.04801010639320102</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>0.1641566265060241</v>
+        <v>0.04716981132075482</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0.01623674977258815</v>
+        <v>-0.07914597815292934</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>0.2563803680981596</v>
+        <v>-0.04240766073871405</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AvePoint, Inc.</t>
+          <t>FORTINET, INC.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Computer Peripheral Equipment, NEC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -62695,53 +62695,53 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>124.495</v>
+        <v>2047.9</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>559.4</v>
+        <v>7730</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4.493353146712719</v>
+        <v>3.774598369060989</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>1.135748423631471</v>
+        <v>1.136725426046194</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>1.212954172132315</v>
+        <v>1.142638062807641</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>1.238689421632597</v>
+        <v>1.144608941728123</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-0.1029409980011255</v>
+        <v>-0.007883515681929465</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.2152943732348467</v>
+        <v>0.1641566265060241</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>-0.1238811389843584</v>
+        <v>0.01623674977258815</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.2203238644160834</v>
+        <v>0.2563803680981596</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>16.89999999999998</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>APG</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>APi Group Corporation</t>
+          <t>AvePoint, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Services-To Dwellings &amp; Other Buildings</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -62750,53 +62750,53 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>2254</v>
+        <v>124.495</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>4066</v>
+        <v>559.4</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>1.803904170363798</v>
+        <v>4.493353146712719</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>1.130434782608696</v>
+        <v>1.135748423631471</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1.029312812491423</v>
+        <v>1.212954172132315</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>0.9956054891189985</v>
+        <v>1.238689421632597</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0.1348292934896971</v>
+        <v>-0.1029409980011255</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0.06775210084033612</v>
+        <v>0.2152943732348467</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.1022230852638824</v>
+        <v>-0.1238811389843584</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0.1326633165829145</v>
+        <v>0.2203238644160834</v>
       </c>
       <c r="O98" s="3" t="n">
-        <v>294</v>
+        <v>16.89999999999998</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>APG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CRANE COMPANY</t>
+          <t>APi Group Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miscellaneous Fabricated Metal Products</t>
+          <t>Services-To Dwellings &amp; Other Buildings</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -62805,53 +62805,53 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>724.7</v>
+        <v>2254</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>1887.3</v>
+        <v>4066</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>2.604250034497033</v>
+        <v>1.803904170363798</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>1.127639023044018</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>1.152222018259438</v>
+        <v>1.029312812491423</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>1.160416349997911</v>
+        <v>0.9956054891189985</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-0.03277732695389224</v>
+        <v>0.1348292934896971</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>0.2963115598598804</v>
+        <v>0.06775210084033612</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-0.03316992162160104</v>
+        <v>-0.1022230852638824</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.2555440055440055</v>
+        <v>0.1326633165829145</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>92.5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APPIAN CORPORATION</t>
+          <t>CRANE COMPANY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Miscellaneous Fabricated Metal Products</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -62860,53 +62860,53 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>203.256</v>
+        <v>724.7</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>625.3</v>
+        <v>1887.3</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>3.076415948360688</v>
+        <v>2.604250034497033</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>1.12398157987956</v>
+        <v>1.127639023044018</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1.091042365684782</v>
+        <v>1.152222018259438</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>1.080062627619855</v>
+        <v>1.160416349997911</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.04391895225970499</v>
+        <v>-0.03277732695389224</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>0.1303326102675342</v>
+        <v>0.2963115598598804</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.02570668851882685</v>
+        <v>-0.03316992162160104</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0.1911392405063292</v>
+        <v>0.2555440055440055</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>25.19999999999993</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
+          <t>APPIAN CORPORATION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Services-Computer Programming Services</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -62915,53 +62915,53 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>5481</v>
+        <v>203.256</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>6939</v>
+        <v>625.3</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1.266009852216749</v>
+        <v>3.076415948360688</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>1.12114577631819</v>
+        <v>1.12398157987956</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>1.03924011239429</v>
+        <v>1.091042365684782</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>1.011938224419658</v>
+        <v>1.080062627619855</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0.1092075518985325</v>
+        <v>0.04391895225970499</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>0.1409075961854653</v>
+        <v>0.1303326102675342</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>0.02574854162708617</v>
+        <v>-0.02570668851882685</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.04499523355576729</v>
+        <v>0.1911392405063292</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>664</v>
+        <v>25.19999999999993</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JOHNSON CONTROLS INTERNATIONAL PLC</t>
+          <t>COGNIZANT TECHNOLOGY SOLUTIONS CORPORATION</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Air-Cond &amp; Warm Air Heatg Equip &amp; Comm &amp; Indl Refrig Equip</t>
+          <t>Services-Computer Programming Services</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -62970,53 +62970,53 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>6614</v>
+        <v>5481</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>27100</v>
+        <v>6939</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>4.097369216812822</v>
+        <v>1.266009852216749</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>1.120955548835803</v>
+        <v>1.12114577631819</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>1.241508377055577</v>
+        <v>1.03924011239429</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>1.223221145200858</v>
+        <v>1.011938224419658</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-0.1022655963650549</v>
+        <v>0.1092075518985325</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>0.2098214285714286</v>
+        <v>0.1409075961854653</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0.01436688311688306</v>
+        <v>0.02574854162708617</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.09286186384666228</v>
+        <v>0.04499523355576729</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>800</v>
+        <v>664</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>STERIS plc</t>
+          <t>JOHNSON CONTROLS INTERNATIONAL PLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
+          <t>Air-Cond &amp; Warm Air Heatg Equip &amp; Comm &amp; Indl Refrig Equip</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -63025,53 +63025,53 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1492.7</v>
+        <v>6614</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1541.4</v>
+        <v>27100</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1.032625443826623</v>
+        <v>4.097369216812822</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>1.117371206538487</v>
+        <v>1.120955548835803</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>1.054410773906568</v>
+        <v>1.241508377055577</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>1.055057723463108</v>
+        <v>1.223221145200858</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0.06231348307537887</v>
+        <v>-0.1022655963650549</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.1549342105263157</v>
+        <v>0.2098214285714286</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>0.02107338887658838</v>
+        <v>0.01436688311688306</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.07303572712242112</v>
+        <v>0.09286186384666228</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>175.2</v>
+        <v>800</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TARGET HOSPITALITY CORP.</t>
+          <t>STERIS plc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hotels, Rooming Houses, Camps &amp; Other Lodging Places</t>
+          <t>Orthopedic, Prosthetic &amp; Surgical Appliances &amp; Supplies</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -63080,53 +63080,53 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>85.455</v>
+        <v>1492.7</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>263.27</v>
+        <v>1541.4</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>3.080802761687438</v>
+        <v>1.032625443826623</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>1.116868527295068</v>
+        <v>1.117371206538487</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>1.396214511575809</v>
+        <v>1.054410773906568</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>1.48932983966939</v>
+        <v>1.055057723463108</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-0.3724613123743221</v>
+        <v>0.06231348307537887</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>0.7089351205738208</v>
+        <v>-0.1549342105263157</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.063535143960467</v>
+        <v>0.02107338887658838</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0.3871213842807517</v>
+        <v>0.07303572712242112</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>9.986999999999995</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>APOGEE ENTERPRISES, INC.</t>
+          <t>TARGET HOSPITALITY CORP.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Glass Products, Made of  Purchased Glass</t>
+          <t>Hotels, Rooming Houses, Camps &amp; Other Lodging Places</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -63135,37 +63135,37 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>342.684</v>
+        <v>85.455</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>737.173</v>
+        <v>263.27</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>2.151174259667799</v>
+        <v>3.080802761687438</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>1.116652659593095</v>
+        <v>1.116868527295068</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>1.091238056438491</v>
+        <v>1.396214511575809</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>1.013426705578402</v>
+        <v>1.48932983966939</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0.1032259540146929</v>
+        <v>-0.3724613123743221</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>-0.1176927514583976</v>
+        <v>0.7089351205738208</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0.08640549223298977</v>
+        <v>0.063535143960467</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>-0.01136107921597584</v>
+        <v>0.3871213842807517</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>39.97500000000002</v>
+        <v>9.986999999999995</v>
       </c>
     </row>
     <row r="106">
@@ -65852,17 +65852,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>MOTOROLA SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -65871,34 +65871,34 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>9289</v>
+        <v>3133</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>64000</v>
+        <v>9500</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>6.889869738400258</v>
+        <v>3.032237472071497</v>
       </c>
       <c r="H155" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.085960275519686</v>
+        <v>1.050872060091059</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.114613700692915</v>
+        <v>1.067829413454745</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-0.1146137006929147</v>
+        <v>-0.0678294134547448</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0.04918032786885251</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>-0.05426794799321644</v>
+        <v>0.01212972420837599</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>0.09346674514420239</v>
+        <v>0.1330922242314647</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>0</v>
@@ -65907,17 +65907,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>COLD</t>
+          <t>RNG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AMERICOLD REALTY TRUST, INC.</t>
+          <t>RingCentral, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -65926,34 +65926,34 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>662.89</v>
+        <v>657.011</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1700</v>
+        <v>2700</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2.564528051411245</v>
+        <v>4.109520236343075</v>
       </c>
       <c r="H156" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.119072189499421</v>
+        <v>1.03880788389923</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.158762919332561</v>
+        <v>1.051743845198973</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-0.1587629193325606</v>
+        <v>-0.05174384519897313</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.03846153846153855</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>-0.09340659340659352</v>
+        <v>0</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>0.01865852833969517</v>
+        <v>0.05901534176448009</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>0</v>
@@ -65962,53 +65962,53 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CTGG</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DOCUSIGN, INC.</t>
+          <t>QWEST CORPORATION</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>875.746</v>
+        <v>1051</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>2.626332292696741</v>
+        <v>1.617507136060894</v>
       </c>
       <c r="H157" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>0.9997616187771211</v>
+        <v>0.9137930393824609</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>0.9996821583694948</v>
+        <v>0.8850573858432812</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0.000317841630505189</v>
+        <v>0.1149426141567188</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>0</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="M157" s="5" t="n">
-        <v>0</v>
+        <v>0.03679653679653683</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>0.09381291872960995</v>
+        <v>-0.1399345335515548</v>
       </c>
       <c r="O157" s="3" t="n">
         <v>0</v>
@@ -66072,53 +66072,53 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CTGG</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>QWEST CORPORATION</t>
+          <t>DOCUSIGN, INC.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>1051</v>
+        <v>875.746</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1.617507136060894</v>
+        <v>2.626332292696741</v>
       </c>
       <c r="H159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>0.9137930393824609</v>
+        <v>0.9997616187771211</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>0.8850573858432812</v>
+        <v>0.9996821583694948</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0.1149426141567188</v>
+        <v>0.000317841630505189</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>-0.1904761904761905</v>
+        <v>0</v>
       </c>
       <c r="M159" s="5" t="n">
-        <v>0.03679653679653683</v>
+        <v>0</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>-0.1399345335515548</v>
+        <v>0.09381291872960995</v>
       </c>
       <c r="O159" s="3" t="n">
         <v>0</v>
@@ -66127,17 +66127,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RYDER SYSTEM, INC.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -66146,34 +66146,34 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>3347</v>
+        <v>9289</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>3400</v>
+        <v>64000</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>1.015835076187631</v>
+        <v>6.889869738400258</v>
       </c>
       <c r="H160" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>1.015760444815641</v>
+        <v>1.085960275519686</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>1.021013926420854</v>
+        <v>1.114613700692915</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-0.02101392642085442</v>
+        <v>-0.1146137006929147</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.04918032786885251</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>0</v>
+        <v>-0.05426794799321644</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>0.04954531201003443</v>
+        <v>0.09346674514420239</v>
       </c>
       <c r="O160" s="3" t="n">
         <v>0</v>
@@ -66182,17 +66182,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KNF</t>
+          <t>COLD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Knife River Corporation</t>
+          <t>AMERICOLD REALTY TRUST, INC.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -66201,34 +66201,34 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>938.587</v>
+        <v>662.89</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1200</v>
+        <v>1700</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1.278517601458362</v>
+        <v>2.564528051411245</v>
       </c>
       <c r="H161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.069950017100908</v>
+        <v>1.119072189499421</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.093266689467878</v>
+        <v>1.158762919332561</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-0.09326668946787797</v>
+        <v>-0.1587629193325606</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>-0.04260411680229781</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>-0.3209678112733748</v>
+        <v>-0.09340659340659352</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.1257293774340067</v>
+        <v>0.01865852833969517</v>
       </c>
       <c r="O161" s="3" t="n">
         <v>0</v>
@@ -66237,17 +66237,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RNG</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RingCentral, Inc.</t>
+          <t>BlackLine, Inc.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -66256,34 +66256,34 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>657.011</v>
+        <v>187.822</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>4.109520236343075</v>
+        <v>5.856608916953285</v>
       </c>
       <c r="H162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>1.03880788389923</v>
+        <v>1.213236048111025</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>1.051743845198973</v>
+        <v>1.284314730814701</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-0.05174384519897313</v>
+        <v>-0.2843147308147007</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.1648840410886372</v>
       </c>
       <c r="M162" s="5" t="n">
-        <v>0</v>
+        <v>-0.03967136846020192</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>0.05901534176448009</v>
+        <v>0.09182967591919766</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>0</v>
@@ -66292,17 +66292,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TRIMBLE INC.</t>
+          <t>Ciena Corp</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Measuring &amp; Controlling Devices, NEC</t>
+          <t>Telephone &amp; Telegraph Apparatus</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -66311,34 +66311,34 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>972</v>
+        <v>1671.129</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>2.05761316872428</v>
+        <v>1.495994623993719</v>
       </c>
       <c r="H163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>1.077335533099608</v>
+        <v>1.089159548671955</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>1.103114044132811</v>
+        <v>1.171168102164085</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-0.1031140441328109</v>
+        <v>-0.1711681021640847</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>0.1764705882352942</v>
+        <v>0.25</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>0</v>
+        <v>-0.2205882352941178</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>0.1099691675231242</v>
+        <v>0.3704687198874841</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>0</v>
@@ -66347,17 +66347,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BlackLine, Inc.</t>
+          <t>TRIMBLE INC.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Measuring &amp; Controlling Devices, NEC</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -66366,34 +66366,34 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>187.822</v>
+        <v>972</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>5.856608916953285</v>
+        <v>2.05761316872428</v>
       </c>
       <c r="H164" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.213236048111025</v>
+        <v>1.077335533099608</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>1.284314730814701</v>
+        <v>1.103114044132811</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-0.2843147308147007</v>
+        <v>-0.1031140441328109</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>0.1648840410886372</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>-0.03967136846020192</v>
+        <v>0</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0.09182967591919766</v>
+        <v>0.1099691675231242</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>0</v>
@@ -66512,17 +66512,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Medpace Holdings, Inc.</t>
+          <t>RYDER SYSTEM, INC.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Services-Commercial Physical &amp; Biological Research</t>
+          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -66531,34 +66531,34 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>707.331</v>
+        <v>3347</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>4.948178434141866</v>
+        <v>1.015835076187631</v>
       </c>
       <c r="H167" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>0.9999078094493223</v>
+        <v>1.015760444815641</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>0.9998770792657633</v>
+        <v>1.021013926420854</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0.0001229207342366978</v>
+        <v>-0.02101392642085442</v>
       </c>
       <c r="L167" s="5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M167" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M167" s="5" t="n">
-        <v>-0.02941176470588225</v>
-      </c>
       <c r="N167" s="5" t="n">
-        <v>0.1724152219999304</v>
+        <v>0.04954531201003443</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>0</v>
@@ -66567,17 +66567,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>KNF</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ciena Corp</t>
+          <t>Knife River Corporation</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Telephone &amp; Telegraph Apparatus</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -66586,34 +66586,34 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1671.129</v>
+        <v>938.587</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1.495994623993719</v>
+        <v>1.278517601458362</v>
       </c>
       <c r="H168" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>1.089159548671955</v>
+        <v>1.069950017100908</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>1.171168102164085</v>
+        <v>1.093266689467878</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-0.1711681021640847</v>
+        <v>-0.09326668946787797</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>0.25</v>
+        <v>-0.04260411680229781</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>-0.2205882352941178</v>
+        <v>-0.3209678112733748</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>0.3704687198874841</v>
+        <v>0.1257293774340067</v>
       </c>
       <c r="O168" s="3" t="n">
         <v>0</v>
@@ -66622,17 +66622,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MOTOROLA SOLUTIONS, INC.</t>
+          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -66641,34 +66641,34 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>3133</v>
+        <v>3161</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>9500</v>
+        <v>28000</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>3.032237472071497</v>
+        <v>8.857956342929453</v>
       </c>
       <c r="H169" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>1.050872060091059</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>1.067829413454745</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-0.0678294134547448</v>
+        <v>-0.2101855938793955</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>0.07954545454545459</v>
+        <v>0.07692307692307687</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>0.01212972420837599</v>
+        <v>0</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>0.1330922242314647</v>
+        <v>0.04575379627485376</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>0</v>
@@ -66677,17 +66677,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
+          <t>Medpace Holdings, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Services-Commercial Physical &amp; Biological Research</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -66696,34 +66696,34 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>3161</v>
+        <v>707.331</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>28000</v>
+        <v>3500</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>8.857956342929453</v>
+        <v>4.948178434141866</v>
       </c>
       <c r="H170" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>0.9999078094493223</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>0.9998770792657633</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-0.2101855938793955</v>
+        <v>0.0001229207342366978</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>0.07692307692307687</v>
+        <v>0</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>0</v>
+        <v>-0.02941176470588225</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>0.04575379627485376</v>
+        <v>0.1724152219999304</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>0</v>

--- a/results/market_bookings_screen.xlsx
+++ b/results/market_bookings_screen.xlsx
@@ -1140,12 +1140,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>SUNC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUNOCO LP</t>
+          <t>SUNOCOCORP LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>1.003716950697805</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1177,12 +1177,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNOCOCORP LLC</t>
+          <t>SUNOCO LP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1203,7 +1203,7 @@
         <v>1.003716950697805</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5179,74 +5179,74 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CQP</t>
+          <t>TOST</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cheniere Energy Partners, L.P.</t>
+          <t>Toast, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2019Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
         <v>1908</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>57400</v>
+        <v>1110</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>30.08385744234801</v>
+        <v>0.5817610062893082</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.6331236897274634</v>
+        <v>1.048218029350105</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TOST</t>
+          <t>CQP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Toast, Inc.</t>
+          <t>Cheniere Energy Partners, L.P.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2019Q4</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
         <v>1908</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>1110</v>
+        <v>57400</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>0.5817610062893082</v>
+        <v>30.08385744234801</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1.048218029350105</v>
+        <v>0.6331236897274634</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>ZAYO GROUP HOLDINGS, INC.</t>
+          <t>ZAYO GROUP LLC</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10474,7 +10474,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>ZAYO GROUP LLC</t>
+          <t>ZAYO GROUP HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11147,33 +11147,33 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>GBTG</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Moderna, Inc.</t>
+          <t>Global Business Travel Group, Inc.</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E299" s="3" t="n">
-        <v>87.22499999999999</v>
+        <v>5</v>
       </c>
       <c r="F299" s="4" t="n">
-        <v>0.1527583187390543</v>
+        <v>0.008756567425569177</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>0.9689667250437828</v>
+        <v>0.9947460595446584</v>
       </c>
       <c r="H299" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -11182,71 +11182,71 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>GBTG</t>
-        </is>
-      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Global Business Travel Group, Inc.</t>
+          <t>NOBLE ENERGY INC</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>5</v>
+        <v>7691</v>
       </c>
       <c r="F300" s="4" t="n">
-        <v>0.008756567425569177</v>
+        <v>13.46935201401051</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>0.9947460595446584</v>
+        <v>4.061295971978984</v>
       </c>
       <c r="H300" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>NOBLE ENERGY INC</t>
+          <t>Moderna, Inc.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2020Q2</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="D301" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>7691</v>
+        <v>87.22499999999999</v>
       </c>
       <c r="F301" s="4" t="n">
-        <v>13.46935201401051</v>
+        <v>0.1527583187390543</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>4.061295971978984</v>
+        <v>0.9689667250437828</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
@@ -13356,71 +13356,71 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>MTB</t>
-        </is>
-      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>M&amp;T BANK CORPORATION</t>
+          <t>AVAYA HOLDINGS CORP.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="D362" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>73</v>
+        <v>1920</v>
       </c>
       <c r="F362" s="4" t="n">
-        <v>0.1746411483253588</v>
+        <v>4.593301435406699</v>
       </c>
       <c r="G362" s="4" t="n">
-        <v>0.9952153110047847</v>
+        <v>0.8038277511961722</v>
       </c>
       <c r="H362" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>failed a data-quality check</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MTB</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>AVAYA HOLDINGS CORP.</t>
+          <t>M&amp;T BANK CORPORATION</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D363" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E363" s="3" t="n">
-        <v>1920</v>
+        <v>73</v>
       </c>
       <c r="F363" s="4" t="n">
-        <v>4.593301435406699</v>
+        <v>0.1746411483253588</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>0.8038277511961722</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="H363" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
@@ -18533,7 +18533,7 @@
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>GRIZZLY MERGER SUB 1, LLC</t>
+          <t>GCI, LLC</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18565,7 +18565,7 @@
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>GCI, LLC</t>
+          <t>GRIZZLY MERGER SUB 1, LLC</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -33095,71 +33095,71 @@
       </c>
     </row>
     <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>CCEL</t>
+        </is>
+      </c>
       <c r="B934" t="inlineStr">
         <is>
+          <t>CRYO-CELL INTERNATIONAL, INC.</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="D934" s="3" t="n">
+        <v>7.824156</v>
+      </c>
+      <c r="E934" s="3" t="n">
+        <v>63.97213</v>
+      </c>
+      <c r="F934" s="4" t="n">
+        <v>8.176233960570315</v>
+      </c>
+      <c r="G934" s="4" t="n">
+        <v>1.153910913841697</v>
+      </c>
+      <c r="H934" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>revenue under $25m/quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="B935" t="inlineStr">
+        <is>
           <t>T2 Biosystems, Inc.</t>
         </is>
       </c>
-      <c r="C934" t="inlineStr">
+      <c r="C935" t="inlineStr">
         <is>
           <t>2020Q4</t>
         </is>
       </c>
-      <c r="D934" s="3" t="n">
+      <c r="D935" s="3" t="n">
         <v>7.788</v>
       </c>
-      <c r="E934" s="3" t="n">
+      <c r="E935" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F934" s="4" t="n">
+      <c r="F935" s="4" t="n">
         <v>0.06420133538777606</v>
       </c>
-      <c r="G934" s="4" t="n">
+      <c r="G935" s="4" t="n">
         <v>1.012840267077555</v>
       </c>
-      <c r="H934" s="4" t="n">
+      <c r="H935" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="I934" t="inlineStr">
+      <c r="I935" t="inlineStr">
         <is>
           <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
-        </is>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr">
-        <is>
-          <t>CCEL</t>
-        </is>
-      </c>
-      <c r="B935" t="inlineStr">
-        <is>
-          <t>CRYO-CELL INTERNATIONAL, INC.</t>
-        </is>
-      </c>
-      <c r="C935" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D935" s="3" t="n">
-        <v>7.776113</v>
-      </c>
-      <c r="E935" s="3" t="n">
-        <v>62.767907</v>
-      </c>
-      <c r="F935" s="4" t="n">
-        <v>8.071887201227657</v>
-      </c>
-      <c r="G935" s="4" t="n">
-        <v>1.168124871642169</v>
-      </c>
-      <c r="H935" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I935" t="inlineStr">
-        <is>
-          <t>revenue under $25m/quarter</t>
         </is>
       </c>
     </row>
@@ -65852,17 +65852,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MOTOROLA SOLUTIONS, INC.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -65871,34 +65871,34 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>3133</v>
+        <v>911.74</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>9500</v>
+        <v>1700</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>3.032237472071497</v>
+        <v>1.864566652773817</v>
       </c>
       <c r="H155" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.050872060091059</v>
+        <v>1.118309234968699</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.067829413454745</v>
+        <v>1.157745646624932</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-0.0678294134547448</v>
+        <v>-0.1577456466249316</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0.07954545454545459</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>0.01212972420837599</v>
+        <v>-0.1887865655471288</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>0.1330922242314647</v>
+        <v>0.1982924719990118</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>0</v>
@@ -65907,17 +65907,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RNG</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RingCentral, Inc.</t>
+          <t>BlackLine, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -65926,34 +65926,34 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>657.011</v>
+        <v>187.822</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>4.109520236343075</v>
+        <v>5.856608916953285</v>
       </c>
       <c r="H156" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.03880788389923</v>
+        <v>1.213236048111025</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.051743845198973</v>
+        <v>1.284314730814701</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-0.05174384519897313</v>
+        <v>-0.2843147308147007</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.1648840410886372</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>0</v>
+        <v>-0.03967136846020192</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>0.05901534176448009</v>
+        <v>0.09182967591919766</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>0</v>
@@ -66017,17 +66017,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp.</t>
+          <t>MOTOROLA SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -66036,34 +66036,34 @@
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>176.1</v>
+        <v>3133</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>800</v>
+        <v>9500</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>4.542873367404884</v>
+        <v>3.032237472071497</v>
       </c>
       <c r="H158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1.480891850388013</v>
+        <v>1.050872060091059</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.641189133850684</v>
+        <v>1.067829413454745</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-0.6411891338506841</v>
+        <v>-0.0678294134547448</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>0</v>
+        <v>0.01212972420837599</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>0.1398058252427183</v>
+        <v>0.1330922242314647</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>0</v>
@@ -66072,17 +66072,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DOCUSIGN, INC.</t>
+          <t>Centrus Energy Corp.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -66091,34 +66091,34 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>875.746</v>
+        <v>176.1</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>2300</v>
+        <v>800</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>2.626332292696741</v>
+        <v>4.542873367404884</v>
       </c>
       <c r="H159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>0.9997616187771211</v>
+        <v>1.480891850388013</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>0.9996821583694948</v>
+        <v>1.641189133850684</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0.000317841630505189</v>
+        <v>-0.6411891338506841</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="M159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>0.09381291872960995</v>
+        <v>0.1398058252427183</v>
       </c>
       <c r="O159" s="3" t="n">
         <v>0</v>
@@ -66182,17 +66182,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>COLD</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AMERICOLD REALTY TRUST, INC.</t>
+          <t>RYDER SYSTEM, INC.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -66201,34 +66201,34 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>662.89</v>
+        <v>3347</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1700</v>
+        <v>3400</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>2.564528051411245</v>
+        <v>1.015835076187631</v>
       </c>
       <c r="H161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.119072189499421</v>
+        <v>1.015760444815641</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.158762919332561</v>
+        <v>1.021013926420854</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-0.1587629193325606</v>
+        <v>-0.02101392642085442</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.0625</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>-0.09340659340659352</v>
+        <v>0</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.01865852833969517</v>
+        <v>0.04954531201003443</v>
       </c>
       <c r="O161" s="3" t="n">
         <v>0</v>
@@ -66237,17 +66237,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>RNG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BlackLine, Inc.</t>
+          <t>RingCentral, Inc.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -66256,34 +66256,34 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>187.822</v>
+        <v>657.011</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>5.856608916953285</v>
+        <v>4.109520236343075</v>
       </c>
       <c r="H162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>1.213236048111025</v>
+        <v>1.03880788389923</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>1.284314730814701</v>
+        <v>1.051743845198973</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-0.2843147308147007</v>
+        <v>-0.05174384519897313</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>0.1648840410886372</v>
+        <v>0.03846153846153855</v>
       </c>
       <c r="M162" s="5" t="n">
-        <v>-0.03967136846020192</v>
+        <v>0</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>0.09182967591919766</v>
+        <v>0.05901534176448009</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>0</v>
@@ -66292,17 +66292,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ciena Corp</t>
+          <t>Medpace Holdings, Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Telephone &amp; Telegraph Apparatus</t>
+          <t>Services-Commercial Physical &amp; Biological Research</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -66311,34 +66311,34 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>1671.129</v>
+        <v>707.331</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>1.495994623993719</v>
+        <v>4.948178434141866</v>
       </c>
       <c r="H163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>1.089159548671955</v>
+        <v>0.9999078094493223</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>1.171168102164085</v>
+        <v>0.9998770792657633</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-0.1711681021640847</v>
+        <v>0.0001229207342366978</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>-0.2205882352941178</v>
+        <v>-0.02941176470588225</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>0.3704687198874841</v>
+        <v>0.1724152219999304</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>0</v>
@@ -66347,17 +66347,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TRIMBLE INC.</t>
+          <t>Ciena Corp</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Measuring &amp; Controlling Devices, NEC</t>
+          <t>Telephone &amp; Telegraph Apparatus</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -66366,34 +66366,34 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>972</v>
+        <v>1671.129</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>2.05761316872428</v>
+        <v>1.495994623993719</v>
       </c>
       <c r="H164" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.077335533099608</v>
+        <v>1.089159548671955</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>1.103114044132811</v>
+        <v>1.171168102164085</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-0.1031140441328109</v>
+        <v>-0.1711681021640847</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>0.1764705882352942</v>
+        <v>0.25</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>0</v>
+        <v>-0.2205882352941178</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0.1099691675231242</v>
+        <v>0.3704687198874841</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>0</v>
@@ -66457,17 +66457,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -66476,34 +66476,34 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>911.74</v>
+        <v>3161</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1700</v>
+        <v>28000</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>1.864566652773817</v>
+        <v>8.857956342929453</v>
       </c>
       <c r="H166" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>1.118309234968699</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>1.157745646624932</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-0.1577456466249316</v>
+        <v>-0.2101855938793955</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.07692307692307687</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>-0.1887865655471288</v>
+        <v>0</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>0.1982924719990118</v>
+        <v>0.04575379627485376</v>
       </c>
       <c r="O166" s="3" t="n">
         <v>0</v>
@@ -66512,17 +66512,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RYDER SYSTEM, INC.</t>
+          <t>TRIMBLE INC.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
+          <t>Measuring &amp; Controlling Devices, NEC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -66531,34 +66531,34 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>3347</v>
+        <v>972</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>3400</v>
+        <v>2000</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>1.015835076187631</v>
+        <v>2.05761316872428</v>
       </c>
       <c r="H167" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1.015760444815641</v>
+        <v>1.077335533099608</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>1.021013926420854</v>
+        <v>1.103114044132811</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-0.02101392642085442</v>
+        <v>-0.1031140441328109</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="M167" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>0.04954531201003443</v>
+        <v>0.1099691675231242</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>0</v>
@@ -66622,17 +66622,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
+          <t>DOCUSIGN, INC.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -66641,34 +66641,34 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>3161</v>
+        <v>875.746</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>28000</v>
+        <v>2300</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>8.857956342929453</v>
+        <v>2.626332292696741</v>
       </c>
       <c r="H169" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>0.9997616187771211</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>0.9996821583694948</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-0.2101855938793955</v>
+        <v>0.000317841630505189</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>0.07692307692307687</v>
+        <v>0</v>
       </c>
       <c r="M169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>0.04575379627485376</v>
+        <v>0.09381291872960995</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>0</v>
@@ -66677,17 +66677,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>COLD</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Medpace Holdings, Inc.</t>
+          <t>AMERICOLD REALTY TRUST, INC.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Services-Commercial Physical &amp; Biological Research</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -66696,34 +66696,34 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>707.331</v>
+        <v>662.89</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>3500</v>
+        <v>1700</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>4.948178434141866</v>
+        <v>2.564528051411245</v>
       </c>
       <c r="H170" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0.9999078094493223</v>
+        <v>1.119072189499421</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>0.9998770792657633</v>
+        <v>1.158762919332561</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0.0001229207342366978</v>
+        <v>-0.1587629193325606</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>0</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>-0.02941176470588225</v>
+        <v>-0.09340659340659352</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>0.1724152219999304</v>
+        <v>0.01865852833969517</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>0</v>

--- a/results/market_bookings_screen.xlsx
+++ b/results/market_bookings_screen.xlsx
@@ -4928,71 +4928,71 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>NCRRP</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CAESARS HOLDINGS, INC.</t>
+          <t>NCR CORP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2018Q1</t>
+          <t>2022Q3</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
         <v>1972</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>150</v>
+        <v>3700</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>0.07606490872210954</v>
+        <v>1.876267748478702</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1.009634888438134</v>
+        <v>0.949290060851927</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>NCRRP</t>
-        </is>
-      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NCR CORP</t>
+          <t>CAESARS HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2018Q1</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
         <v>1972</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>3700</v>
+        <v>150</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1.876267748478702</v>
+        <v>0.07606490872210954</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0.949290060851927</v>
+        <v>1.009634888438134</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>ZAYO GROUP LLC</t>
+          <t>ZAYO GROUP HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10474,7 +10474,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>ZAYO GROUP HOLDINGS, INC.</t>
+          <t>ZAYO GROUP LLC</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11145,104 +11145,104 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>GBTG</t>
-        </is>
-      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Global Business Travel Group, Inc.</t>
+          <t>NOBLE ENERGY INC</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2020Q2</t>
         </is>
       </c>
       <c r="D299" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E299" s="3" t="n">
-        <v>5</v>
+        <v>7691</v>
       </c>
       <c r="F299" s="4" t="n">
-        <v>0.008756567425569177</v>
+        <v>13.46935201401051</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>0.9947460595446584</v>
+        <v>4.061295971978984</v>
       </c>
       <c r="H299" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>NOBLE ENERGY INC</t>
+          <t>Moderna, Inc.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2020Q2</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>7691</v>
+        <v>87.22499999999999</v>
       </c>
       <c r="F300" s="4" t="n">
-        <v>13.46935201401051</v>
+        <v>0.1527583187390543</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>4.061295971978984</v>
+        <v>0.9689667250437828</v>
       </c>
       <c r="H300" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>GBTG</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Moderna, Inc.</t>
+          <t>Global Business Travel Group, Inc.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="D301" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>87.22499999999999</v>
+        <v>5</v>
       </c>
       <c r="F301" s="4" t="n">
-        <v>0.1527583187390543</v>
+        <v>0.008756567425569177</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>0.9689667250437828</v>
+        <v>0.9947460595446584</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -13356,71 +13356,71 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>MTB</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AVAYA HOLDINGS CORP.</t>
+          <t>M&amp;T BANK CORPORATION</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D362" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>1920</v>
+        <v>73</v>
       </c>
       <c r="F362" s="4" t="n">
-        <v>4.593301435406699</v>
+        <v>0.1746411483253588</v>
       </c>
       <c r="G362" s="4" t="n">
-        <v>0.8038277511961722</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="H362" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>MTB</t>
-        </is>
-      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>M&amp;T BANK CORPORATION</t>
+          <t>AVAYA HOLDINGS CORP.</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="D363" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E363" s="3" t="n">
-        <v>73</v>
+        <v>1920</v>
       </c>
       <c r="F363" s="4" t="n">
-        <v>0.1746411483253588</v>
+        <v>4.593301435406699</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>0.9952153110047847</v>
+        <v>0.8038277511961722</v>
       </c>
       <c r="H363" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>failed a data-quality check</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
@@ -18533,7 +18533,7 @@
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>GCI, LLC</t>
+          <t>GRIZZLY MERGER SUB 1, LLC</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18565,7 +18565,7 @@
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>GRIZZLY MERGER SUB 1, LLC</t>
+          <t>GCI, LLC</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -27768,7 +27768,7 @@
     <row r="782">
       <c r="B782" t="inlineStr">
         <is>
-          <t>MN8 Energy Holdings LLC</t>
+          <t>GREENBACKER RENEWABLE ENERGY COMPANY LLC</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -27789,7 +27789,7 @@
         <v>1.000119374477737</v>
       </c>
       <c r="H782" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
     <row r="783">
       <c r="B783" t="inlineStr">
         <is>
-          <t>GREENBACKER RENEWABLE ENERGY COMPANY LLC</t>
+          <t>MN8 Energy Holdings LLC</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -27821,7 +27821,7 @@
         <v>1.000119374477737</v>
       </c>
       <c r="H783" s="4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
@@ -29072,136 +29072,141 @@
       </c>
     </row>
     <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>WINA</t>
+        </is>
+      </c>
       <c r="B820" t="inlineStr">
         <is>
+          <t>WINMARK CORPORATION</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="D820" s="3" t="n">
+        <v>27.8905</v>
+      </c>
+      <c r="E820" s="3" t="n">
+        <v>10.1143</v>
+      </c>
+      <c r="F820" s="4" t="n">
+        <v>0.3626431939190764</v>
+      </c>
+      <c r="G820" s="4" t="n">
+        <v>1.00099675516753</v>
+      </c>
+      <c r="H820" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="B821" t="inlineStr">
+        <is>
           <t>TERRAN ORBITAL CORPORATION</t>
         </is>
       </c>
-      <c r="C820" t="inlineStr">
+      <c r="C821" t="inlineStr">
         <is>
           <t>2024Q1</t>
         </is>
       </c>
-      <c r="D820" s="3" t="n">
+      <c r="D821" s="3" t="n">
         <v>27.235</v>
       </c>
-      <c r="E820" s="3" t="n">
+      <c r="E821" s="3" t="n">
         <v>2700</v>
       </c>
-      <c r="F820" s="4" t="n">
+      <c r="F821" s="4" t="n">
         <v>99.13713970993207</v>
       </c>
-      <c r="G820" s="4" t="n">
+      <c r="G821" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H820" s="4" t="n">
+      <c r="H821" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I820" t="inlineStr">
+      <c r="I821" t="inlineStr">
         <is>
           <t>failed a data-quality check</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>RDVT</t>
-        </is>
-      </c>
-      <c r="B821" t="inlineStr">
-        <is>
-          <t>RED VIOLET, INC.</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D821" s="3" t="n">
-        <v>26.718</v>
-      </c>
-      <c r="E821" s="3" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="F821" s="4" t="n">
-        <v>0.8896623998802305</v>
-      </c>
-      <c r="G821" s="4" t="n">
-        <v>1.059622726251965</v>
-      </c>
-      <c r="H821" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
+          <t>RDVT</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>RED VIOLET, INC.</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D822" s="3" t="n">
+        <v>26.718</v>
+      </c>
+      <c r="E822" s="3" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="F822" s="4" t="n">
+        <v>0.8896623998802305</v>
+      </c>
+      <c r="G822" s="4" t="n">
+        <v>1.059622726251965</v>
+      </c>
+      <c r="H822" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
           <t>MTEX</t>
         </is>
       </c>
-      <c r="B822" t="inlineStr">
+      <c r="B823" t="inlineStr">
         <is>
           <t>MANNATECH INC</t>
         </is>
       </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D822" s="3" t="n">
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D823" s="3" t="n">
         <v>26.65</v>
       </c>
-      <c r="E822" s="3" t="n">
+      <c r="E823" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F822" s="4" t="n">
+      <c r="F823" s="4" t="n">
         <v>0.00375234521575985</v>
       </c>
-      <c r="G822" s="4" t="n">
+      <c r="G823" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H822" s="4" t="n">
+      <c r="H823" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="I822" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
-        </is>
-      </c>
-    </row>
-    <row r="823">
-      <c r="B823" t="inlineStr">
-        <is>
-          <t>PORTOLA PHARMACEUTICALS INC</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>2020Q1</t>
-        </is>
-      </c>
-      <c r="D823" s="3" t="n">
-        <v>26.389</v>
-      </c>
-      <c r="E823" s="3" t="n">
-        <v>4.423</v>
-      </c>
-      <c r="F823" s="4" t="n">
-        <v>0.1676077153359354</v>
-      </c>
-      <c r="G823" s="4" t="n">
-        <v>0.9714653833036493</v>
-      </c>
-      <c r="H823" s="4" t="n">
-        <v>9</v>
       </c>
       <c r="I823" t="inlineStr">
         <is>
@@ -29212,28 +29217,28 @@
     <row r="824">
       <c r="B824" t="inlineStr">
         <is>
-          <t>EDGEWATER TECHNOLOGY INC/DE/</t>
+          <t>PORTOLA PHARMACEUTICALS INC</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>2018Q2</t>
+          <t>2020Q1</t>
         </is>
       </c>
       <c r="D824" s="3" t="n">
-        <v>26.334</v>
+        <v>26.389</v>
       </c>
       <c r="E824" s="3" t="n">
-        <v>0.908</v>
+        <v>4.423</v>
       </c>
       <c r="F824" s="4" t="n">
-        <v>0.03448013974329764</v>
+        <v>0.1676077153359354</v>
       </c>
       <c r="G824" s="4" t="n">
-        <v>1.019974177868915</v>
+        <v>0.9714653833036493</v>
       </c>
       <c r="H824" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I824" t="inlineStr">
         <is>
@@ -29244,102 +29249,97 @@
     <row r="825">
       <c r="B825" t="inlineStr">
         <is>
+          <t>EDGEWATER TECHNOLOGY INC/DE/</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="D825" s="3" t="n">
+        <v>26.334</v>
+      </c>
+      <c r="E825" s="3" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="F825" s="4" t="n">
+        <v>0.03448013974329764</v>
+      </c>
+      <c r="G825" s="4" t="n">
+        <v>1.019974177868915</v>
+      </c>
+      <c r="H825" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="B826" t="inlineStr">
+        <is>
           <t>Venus Concept Inc.</t>
         </is>
       </c>
-      <c r="C825" t="inlineStr">
+      <c r="C826" t="inlineStr">
         <is>
           <t>2019Q3</t>
         </is>
       </c>
-      <c r="D825" s="3" t="n">
+      <c r="D826" s="3" t="n">
         <v>26.154</v>
       </c>
-      <c r="E825" s="3" t="n">
+      <c r="E826" s="3" t="n">
         <v>1.602</v>
       </c>
-      <c r="F825" s="4" t="n">
+      <c r="F826" s="4" t="n">
         <v>0.06125258086717137</v>
       </c>
-      <c r="G825" s="4" t="n">
+      <c r="G826" s="4" t="n">
         <v>1.002561749636767</v>
       </c>
-      <c r="H825" s="4" t="n">
+      <c r="H826" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I825" t="inlineStr">
+      <c r="I826" t="inlineStr">
         <is>
           <t>failed a data-quality check</t>
-        </is>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" t="inlineStr">
-        <is>
-          <t>BOXL</t>
-        </is>
-      </c>
-      <c r="B826" t="inlineStr">
-        <is>
-          <t>BOXLIGHT CORPORATION</t>
-        </is>
-      </c>
-      <c r="C826" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D826" s="3" t="n">
-        <v>25.918</v>
-      </c>
-      <c r="E826" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F826" s="4" t="n">
-        <v>0.8758391851223088</v>
-      </c>
-      <c r="G826" s="4" t="n">
-        <v>0.9807083879929007</v>
-      </c>
-      <c r="H826" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I826" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>BOXL</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>TransMedics Group, Inc.</t>
+          <t>BOXLIGHT CORPORATION</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D827" s="3" t="n">
-        <v>25.683</v>
+        <v>25.918</v>
       </c>
       <c r="E827" s="3" t="n">
-        <v>1.6</v>
+        <v>22.7</v>
       </c>
       <c r="F827" s="4" t="n">
-        <v>0.06229801814429779</v>
+        <v>0.8758391851223088</v>
       </c>
       <c r="G827" s="4" t="n">
-        <v>0.9961063738659813</v>
+        <v>0.9807083879929007</v>
       </c>
       <c r="H827" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I827" t="inlineStr">
         <is>
@@ -29350,346 +29350,346 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
+          <t>TMDX</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>TransMedics Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="D828" s="3" t="n">
+        <v>25.683</v>
+      </c>
+      <c r="E828" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F828" s="4" t="n">
+        <v>0.06229801814429779</v>
+      </c>
+      <c r="G828" s="4" t="n">
+        <v>0.9961063738659813</v>
+      </c>
+      <c r="H828" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
           <t>BTBT</t>
         </is>
       </c>
-      <c r="B828" t="inlineStr">
+      <c r="B829" t="inlineStr">
         <is>
           <t>BIT     DIGITAL, INC.</t>
         </is>
       </c>
-      <c r="C828" t="inlineStr">
+      <c r="C829" t="inlineStr">
         <is>
           <t>2025Q2</t>
         </is>
       </c>
-      <c r="D828" s="3" t="n">
+      <c r="D829" s="3" t="n">
         <v>25.659</v>
       </c>
-      <c r="E828" s="3" t="n">
+      <c r="E829" s="3" t="n">
         <v>13.852674</v>
       </c>
-      <c r="F828" s="4" t="n">
+      <c r="F829" s="4" t="n">
         <v>0.5398758330410383</v>
       </c>
-      <c r="G828" s="4" t="n">
+      <c r="G829" s="4" t="n">
         <v>1.123789430609143</v>
       </c>
-      <c r="H828" s="4" t="n">
+      <c r="H829" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I828" t="inlineStr">
+      <c r="I829" t="inlineStr">
         <is>
           <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
-    <row r="829">
-      <c r="B829" t="inlineStr">
+    <row r="830">
+      <c r="B830" t="inlineStr">
         <is>
           <t>DECISIONPOINT SYSTEMS, Inc.</t>
         </is>
       </c>
-      <c r="C829" t="inlineStr">
+      <c r="C830" t="inlineStr">
         <is>
           <t>2024Q1</t>
         </is>
       </c>
-      <c r="D829" s="3" t="n">
+      <c r="D830" s="3" t="n">
         <v>25.618</v>
       </c>
-      <c r="E829" s="3" t="n">
+      <c r="E830" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="F829" s="4" t="n">
+      <c r="F830" s="4" t="n">
         <v>0.5660082754313374</v>
       </c>
-      <c r="G829" s="4" t="n">
+      <c r="G830" s="4" t="n">
         <v>1.042938558825826</v>
-      </c>
-      <c r="H829" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I829" t="inlineStr">
-        <is>
-          <t>failed a data-quality check</t>
-        </is>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>GEOS</t>
-        </is>
-      </c>
-      <c r="B830" t="inlineStr">
-        <is>
-          <t>GEOSPACE TECHNOLOGIES CORP</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>2025Q4</t>
-        </is>
-      </c>
-      <c r="D830" s="3" t="n">
-        <v>25.586</v>
-      </c>
-      <c r="E830" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="F830" s="4" t="n">
-        <v>3.634800281403893</v>
-      </c>
-      <c r="G830" s="4" t="n">
-        <v>1.03908387399359</v>
       </c>
       <c r="H830" s="4" t="n">
         <v>4</v>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>GEOS</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Jerash Holdings (US), Inc.</t>
+          <t>GEOSPACE TECHNOLOGIES CORP</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>2019Q4</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="D831" s="3" t="n">
-        <v>25.446708</v>
+        <v>25.586</v>
       </c>
       <c r="E831" s="3" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F831" s="4" t="n">
-        <v>0</v>
+        <v>3.634800281403893</v>
       </c>
       <c r="G831" s="4" t="n">
-        <v>1</v>
+        <v>1.03908387399359</v>
       </c>
       <c r="H831" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>UUUU</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>ENERGY FUELS INC.</t>
+          <t>Jerash Holdings (US), Inc.</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2019Q4</t>
         </is>
       </c>
       <c r="D832" s="3" t="n">
-        <v>25.108</v>
+        <v>25.446708</v>
       </c>
       <c r="E832" s="3" t="n">
-        <v>165.93</v>
+        <v>0</v>
       </c>
       <c r="F832" s="4" t="n">
-        <v>6.608650629281504</v>
+        <v>0</v>
       </c>
       <c r="G832" s="4" t="n">
-        <v>0.7012904253624342</v>
+        <v>1</v>
       </c>
       <c r="H832" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I832" t="inlineStr">
         <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>UUUU</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>ENERGY FUELS INC.</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D833" s="3" t="n">
+        <v>25.108</v>
+      </c>
+      <c r="E833" s="3" t="n">
+        <v>165.93</v>
+      </c>
+      <c r="F833" s="4" t="n">
+        <v>6.608650629281504</v>
+      </c>
+      <c r="G833" s="4" t="n">
+        <v>0.7012904253624342</v>
+      </c>
+      <c r="H833" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
           <t>under 5 quarters of RPO history</t>
         </is>
       </c>
     </row>
-    <row r="833">
-      <c r="B833" t="inlineStr">
+    <row r="834">
+      <c r="B834" t="inlineStr">
         <is>
           <t>LOGILITY SUPPLY CHAIN SOLUTIONS, INC.</t>
         </is>
       </c>
-      <c r="C833" t="inlineStr">
+      <c r="C834" t="inlineStr">
         <is>
           <t>2024Q4</t>
         </is>
       </c>
-      <c r="D833" s="3" t="n">
+      <c r="D834" s="3" t="n">
         <v>25.007</v>
       </c>
-      <c r="E833" s="3" t="n">
+      <c r="E834" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="F833" s="4" t="n">
+      <c r="F834" s="4" t="n">
         <v>4.43875714799856</v>
       </c>
-      <c r="G833" s="4" t="n">
+      <c r="G834" s="4" t="n">
         <v>0.6401007717839006</v>
       </c>
-      <c r="H833" s="4" t="n">
+      <c r="H834" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="I833" t="inlineStr">
+      <c r="I834" t="inlineStr">
         <is>
           <t>no recent filing</t>
         </is>
       </c>
     </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
+    <row r="835">
+      <c r="A835" t="inlineStr">
         <is>
           <t>CXDO</t>
         </is>
       </c>
-      <c r="B834" t="inlineStr">
+      <c r="B835" t="inlineStr">
         <is>
           <t>Crexendo, Inc.</t>
         </is>
       </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D834" s="3" t="n">
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D835" s="3" t="n">
         <v>24.646</v>
       </c>
-      <c r="E834" s="3" t="n">
+      <c r="E835" s="3" t="n">
         <v>138.971</v>
       </c>
-      <c r="F834" s="4" t="n">
+      <c r="F835" s="4" t="n">
         <v>5.638683762070924</v>
       </c>
-      <c r="G834" s="4" t="n">
+      <c r="G835" s="4" t="n">
         <v>1.137547675079121</v>
       </c>
-      <c r="H834" s="4" t="n">
+      <c r="H835" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I834" t="inlineStr">
+      <c r="I835" t="inlineStr">
         <is>
           <t>revenue under $25m/quarter</t>
-        </is>
-      </c>
-    </row>
-    <row r="835">
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>JAMBA, INC.</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>2018Q2</t>
-        </is>
-      </c>
-      <c r="D835" s="3" t="n">
-        <v>24.493</v>
-      </c>
-      <c r="E835" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F835" s="4" t="n">
-        <v>0.2245539541909934</v>
-      </c>
-      <c r="G835" s="4" t="n">
-        <v>1.004082799167109</v>
-      </c>
-      <c r="H835" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I835" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="B836" t="inlineStr">
         <is>
+          <t>JAMBA, INC.</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="D836" s="3" t="n">
+        <v>24.493</v>
+      </c>
+      <c r="E836" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F836" s="4" t="n">
+        <v>0.2245539541909934</v>
+      </c>
+      <c r="G836" s="4" t="n">
+        <v>1.004082799167109</v>
+      </c>
+      <c r="H836" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="B837" t="inlineStr">
+        <is>
           <t>EMCORE Corporation</t>
         </is>
       </c>
-      <c r="C836" t="inlineStr">
+      <c r="C837" t="inlineStr">
         <is>
           <t>2019Q3</t>
         </is>
       </c>
-      <c r="D836" s="3" t="n">
+      <c r="D837" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="E836" s="3" t="n">
+      <c r="E837" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="F836" s="4" t="n">
+      <c r="F837" s="4" t="n">
         <v>0.06995884773662552</v>
       </c>
-      <c r="G836" s="4" t="n">
+      <c r="G837" s="4" t="n">
         <v>0.9958847736625513</v>
       </c>
-      <c r="H836" s="4" t="n">
+      <c r="H837" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="I836" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
-        </is>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>VERI</t>
-        </is>
-      </c>
-      <c r="B837" t="inlineStr">
-        <is>
-          <t>Veritone, Inc.</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D837" s="3" t="n">
-        <v>24.263</v>
-      </c>
-      <c r="E837" s="3" t="n">
-        <v>20.618</v>
-      </c>
-      <c r="F837" s="4" t="n">
-        <v>0.8497712566459217</v>
-      </c>
-      <c r="G837" s="4" t="n">
-        <v>0.8373655360013188</v>
-      </c>
-      <c r="H837" s="4" t="n">
-        <v>27</v>
       </c>
       <c r="I837" t="inlineStr">
         <is>
@@ -29700,12 +29700,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>VERI</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Arteris, Inc.</t>
+          <t>Veritone, Inc.</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -29714,56 +29714,56 @@
         </is>
       </c>
       <c r="D838" s="3" t="n">
-        <v>24.134</v>
+        <v>24.263</v>
       </c>
       <c r="E838" s="3" t="n">
-        <v>131.4</v>
+        <v>20.618</v>
       </c>
       <c r="F838" s="4" t="n">
-        <v>5.44460097787354</v>
+        <v>0.8497712566459217</v>
       </c>
       <c r="G838" s="4" t="n">
-        <v>1.683682771194166</v>
+        <v>0.8373655360013188</v>
       </c>
       <c r="H838" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>revenue under $25m/quarter</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>AIP</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>ALLOT LTD.</t>
+          <t>Arteris, Inc.</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D839" s="3" t="n">
-        <v>24.051</v>
+        <v>24.134</v>
       </c>
       <c r="E839" s="3" t="n">
-        <v>93.783</v>
+        <v>131.4</v>
       </c>
       <c r="F839" s="4" t="n">
-        <v>3.899338904827242</v>
+        <v>5.44460097787354</v>
       </c>
       <c r="G839" s="4" t="n">
-        <v>2.20340110598312</v>
+        <v>1.683682771194166</v>
       </c>
       <c r="H839" s="4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I839" t="inlineStr">
         <is>
@@ -29774,118 +29774,118 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
+          <t>ALLT</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>ALLOT LTD.</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="D840" s="3" t="n">
+        <v>24.051</v>
+      </c>
+      <c r="E840" s="3" t="n">
+        <v>93.783</v>
+      </c>
+      <c r="F840" s="4" t="n">
+        <v>3.899338904827242</v>
+      </c>
+      <c r="G840" s="4" t="n">
+        <v>2.20340110598312</v>
+      </c>
+      <c r="H840" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>revenue under $25m/quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
           <t>SSTI</t>
         </is>
       </c>
-      <c r="B840" t="inlineStr">
+      <c r="B841" t="inlineStr">
         <is>
           <t>SoundThinking, Inc.</t>
         </is>
       </c>
-      <c r="C840" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D840" s="3" t="n">
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D841" s="3" t="n">
         <v>23.889</v>
       </c>
-      <c r="E840" s="3" t="n">
+      <c r="E841" s="3" t="n">
         <v>93.084</v>
       </c>
-      <c r="F840" s="4" t="n">
+      <c r="F841" s="4" t="n">
         <v>3.896521411528319</v>
       </c>
-      <c r="G840" s="4" t="n">
+      <c r="G841" s="4" t="n">
         <v>0.9980744275608023</v>
       </c>
-      <c r="H840" s="4" t="n">
+      <c r="H841" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I840" t="inlineStr">
+      <c r="I841" t="inlineStr">
         <is>
           <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
-    <row r="841">
-      <c r="B841" t="inlineStr">
+    <row r="842">
+      <c r="B842" t="inlineStr">
         <is>
           <t>AROTECH CORP</t>
         </is>
       </c>
-      <c r="C841" t="inlineStr">
+      <c r="C842" t="inlineStr">
         <is>
           <t>2018Q4</t>
         </is>
       </c>
-      <c r="D841" s="3" t="n">
+      <c r="D842" s="3" t="n">
         <v>23.632</v>
       </c>
-      <c r="E841" s="3" t="n">
+      <c r="E842" s="3" t="n">
         <v>64.8</v>
       </c>
-      <c r="F841" s="4" t="n">
+      <c r="F842" s="4" t="n">
         <v>2.742044685172647</v>
       </c>
-      <c r="G841" s="4" t="n">
+      <c r="G842" s="4" t="n">
         <v>0.7503385240352063</v>
       </c>
-      <c r="H841" s="4" t="n">
+      <c r="H842" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I841" t="inlineStr">
+      <c r="I842" t="inlineStr">
         <is>
           <t>revenue under $25m/quarter</t>
-        </is>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>CURI</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>CURIOSITYSTREAM INC.</t>
-        </is>
-      </c>
-      <c r="C842" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="D842" s="3" t="n">
-        <v>23.245</v>
-      </c>
-      <c r="E842" s="3" t="n">
-        <v>3.018</v>
-      </c>
-      <c r="F842" s="4" t="n">
-        <v>0.1298343729834373</v>
-      </c>
-      <c r="G842" s="4" t="n">
-        <v>0.9885136588513659</v>
-      </c>
-      <c r="H842" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I842" t="inlineStr">
-        <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>RYM</t>
+          <t>CURI</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>RYTHM INC.</t>
+          <t>CURIOSITYSTREAM INC.</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -29894,56 +29894,56 @@
         </is>
       </c>
       <c r="D843" s="3" t="n">
-        <v>23.021</v>
+        <v>23.245</v>
       </c>
       <c r="E843" s="3" t="n">
-        <v>290.9</v>
+        <v>3.018</v>
       </c>
       <c r="F843" s="4" t="n">
-        <v>12.63628860605534</v>
+        <v>0.1298343729834373</v>
       </c>
       <c r="G843" s="4" t="n">
-        <v>0.2398245080578602</v>
+        <v>0.9885136588513659</v>
       </c>
       <c r="H843" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>failed a data-quality check</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>VASO</t>
+          <t>RYM</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>VASO CORPORATION</t>
+          <t>RYTHM INC.</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D844" s="3" t="n">
-        <v>22.95</v>
+        <v>23.021</v>
       </c>
       <c r="E844" s="3" t="n">
-        <v>0.005</v>
+        <v>290.9</v>
       </c>
       <c r="F844" s="4" t="n">
-        <v>0.0002178649237472767</v>
+        <v>12.63628860605534</v>
       </c>
       <c r="G844" s="4" t="n">
-        <v>0.6254901960784314</v>
+        <v>0.2398245080578602</v>
       </c>
       <c r="H844" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I844" t="inlineStr">
         <is>
@@ -29954,70 +29954,70 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>CEPL</t>
+          <t>VASO</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Capstone Energy Plus, Inc.</t>
+          <t>VASO CORPORATION</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="D845" s="3" t="n">
-        <v>22.9</v>
+        <v>22.95</v>
       </c>
       <c r="E845" s="3" t="n">
-        <v>4.9</v>
+        <v>0.005</v>
       </c>
       <c r="F845" s="4" t="n">
-        <v>0.2139737991266376</v>
+        <v>0.0002178649237472767</v>
       </c>
       <c r="G845" s="4" t="n">
-        <v>1.039301310043668</v>
+        <v>0.6254901960784314</v>
       </c>
       <c r="H845" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I845" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>NPCE</t>
+          <t>CEPL</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>NEUROPACE, INC.</t>
+          <t>Capstone Energy Plus, Inc.</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="D846" s="3" t="n">
-        <v>22.826</v>
+        <v>22.9</v>
       </c>
       <c r="E846" s="3" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="F846" s="4" t="n">
-        <v>0.07009550512573381</v>
+        <v>0.2139737991266376</v>
       </c>
       <c r="G846" s="4" t="n">
-        <v>0.9868570927889249</v>
+        <v>1.039301310043668</v>
       </c>
       <c r="H846" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I846" t="inlineStr">
         <is>
@@ -30028,12 +30028,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>NPCE</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>HARVARD BIOSCIENCE, INC.</t>
+          <t>NEUROPACE, INC.</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -30042,19 +30042,19 @@
         </is>
       </c>
       <c r="D847" s="3" t="n">
-        <v>22.727</v>
+        <v>22.826</v>
       </c>
       <c r="E847" s="3" t="n">
-        <v>2.316</v>
+        <v>1.6</v>
       </c>
       <c r="F847" s="4" t="n">
-        <v>0.1019052228626743</v>
+        <v>0.07009550512573381</v>
       </c>
       <c r="G847" s="4" t="n">
-        <v>1.005720068640824</v>
+        <v>0.9868570927889249</v>
       </c>
       <c r="H847" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I847" t="inlineStr">
         <is>
@@ -30065,95 +30065,95 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>eGain Corporation</t>
+          <t>HARVARD BIOSCIENCE, INC.</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D848" s="3" t="n">
-        <v>22.499</v>
+        <v>22.727</v>
       </c>
       <c r="E848" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>2.316</v>
       </c>
       <c r="F848" s="4" t="n">
-        <v>3.293479710209342</v>
+        <v>0.1019052228626743</v>
       </c>
       <c r="G848" s="4" t="n">
-        <v>0.5199786657184758</v>
+        <v>1.005720068640824</v>
       </c>
       <c r="H848" s="4" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="I848" t="inlineStr">
         <is>
-          <t>revenue under $25m/quarter</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>BGSF</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>BGSF, INC</t>
+          <t>eGain Corporation</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D849" s="3" t="n">
-        <v>22.313</v>
+        <v>22.499</v>
       </c>
       <c r="E849" s="3" t="n">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F849" s="4" t="n">
-        <v>0</v>
+        <v>3.293479710209342</v>
       </c>
       <c r="G849" s="4" t="n">
-        <v>1</v>
+        <v>0.5199786657184758</v>
       </c>
       <c r="H849" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>failed a data-quality check</t>
+          <t>revenue under $25m/quarter</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>BGSF</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>NATURAL GAS SERVICES GROUP, INC.</t>
+          <t>BGSF, INC</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D850" s="3" t="n">
-        <v>22.043</v>
+        <v>22.313</v>
       </c>
       <c r="E850" s="3" t="n">
         <v>0</v>
@@ -30165,44 +30165,44 @@
         <v>1</v>
       </c>
       <c r="H850" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I850" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>WINA</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>WINMARK CORPORATION</t>
+          <t>NATURAL GAS SERVICES GROUP, INC.</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2022Q3</t>
         </is>
       </c>
       <c r="D851" s="3" t="n">
-        <v>21.966</v>
+        <v>22.043</v>
       </c>
       <c r="E851" s="3" t="n">
-        <v>10.0865</v>
+        <v>0</v>
       </c>
       <c r="F851" s="4" t="n">
-        <v>0.4591869252481107</v>
+        <v>0</v>
       </c>
       <c r="G851" s="4" t="n">
-        <v>1.005681507784758</v>
+        <v>1</v>
       </c>
       <c r="H851" s="4" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I851" t="inlineStr">
         <is>
@@ -37001,143 +37001,143 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
+          <t>BABB</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>BAB, Inc.</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="D1046" s="3" t="n">
+        <v>0.907867</v>
+      </c>
+      <c r="E1046" s="3" t="n">
+        <v>0.183804</v>
+      </c>
+      <c r="F1046" s="4" t="n">
+        <v>0.2024569678157704</v>
+      </c>
+      <c r="G1046" s="4" t="n">
+        <v>1.007311643665867</v>
+      </c>
+      <c r="H1046" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
           <t>ONAR</t>
         </is>
       </c>
-      <c r="B1046" t="inlineStr">
+      <c r="B1047" t="inlineStr">
         <is>
           <t>ONAR Holding Corporation</t>
         </is>
       </c>
-      <c r="C1046" t="inlineStr">
+      <c r="C1047" t="inlineStr">
         <is>
           <t>2024Q3</t>
         </is>
       </c>
-      <c r="D1046" s="3" t="n">
+      <c r="D1047" s="3" t="n">
         <v>0.898797</v>
       </c>
-      <c r="E1046" s="3" t="n">
+      <c r="E1047" s="3" t="n">
         <v>0.426226</v>
       </c>
-      <c r="F1046" s="4" t="n">
+      <c r="F1047" s="4" t="n">
         <v>0.4742183162605127</v>
       </c>
-      <c r="G1046" s="4" t="n">
+      <c r="G1047" s="4" t="n">
         <v>1.081638011697858</v>
       </c>
-      <c r="H1046" s="4" t="n">
+      <c r="H1047" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I1046" t="inlineStr">
+      <c r="I1047" t="inlineStr">
         <is>
           <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
-    <row r="1047">
-      <c r="B1047" t="inlineStr">
+    <row r="1048">
+      <c r="B1048" t="inlineStr">
         <is>
           <t>INFINITE GROUP, INC.</t>
         </is>
       </c>
-      <c r="C1047" t="inlineStr">
+      <c r="C1048" t="inlineStr">
         <is>
           <t>2025Q3</t>
         </is>
       </c>
-      <c r="D1047" s="3" t="n">
+      <c r="D1048" s="3" t="n">
         <v>0.8346710000000001</v>
       </c>
-      <c r="E1047" s="3" t="n">
+      <c r="E1048" s="3" t="n">
         <v>0.209</v>
       </c>
-      <c r="F1047" s="4" t="n">
+      <c r="F1048" s="4" t="n">
         <v>0.2503980610324307</v>
       </c>
-      <c r="G1047" s="4" t="n">
+      <c r="G1048" s="4" t="n">
         <v>0.9675321174450772</v>
       </c>
-      <c r="H1047" s="4" t="n">
+      <c r="H1048" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="I1047" t="inlineStr">
+      <c r="I1048" t="inlineStr">
         <is>
           <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>OPTT</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>OCEAN POWER TECHNOLOGIES, INC.</t>
-        </is>
-      </c>
-      <c r="C1048" t="inlineStr">
-        <is>
-          <t>2024Q4</t>
-        </is>
-      </c>
-      <c r="D1048" s="3" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E1048" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F1048" s="4" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="G1048" s="4" t="n">
-        <v>5.484848484848485</v>
-      </c>
-      <c r="H1048" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I1048" t="inlineStr">
-        <is>
-          <t>revenue under $25m/quarter</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>BABB</t>
+          <t>OPTT</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>BAB, INC.</t>
+          <t>OCEAN POWER TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2024Q4</t>
         </is>
       </c>
       <c r="D1049" s="3" t="n">
-        <v>0.803689</v>
+        <v>0.825</v>
       </c>
       <c r="E1049" s="3" t="n">
-        <v>0.177166</v>
+        <v>7.5</v>
       </c>
       <c r="F1049" s="4" t="n">
-        <v>0.2204409914780469</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="G1049" s="4" t="n">
-        <v>1.04666979391282</v>
+        <v>5.484848484848485</v>
       </c>
       <c r="H1049" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I1049" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>revenue under $25m/quarter</t>
         </is>
       </c>
     </row>
@@ -65852,17 +65852,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Ciena Corp</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Telephone &amp; Telegraph Apparatus</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -65871,34 +65871,34 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>911.74</v>
+        <v>1671.129</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>1700</v>
+        <v>2500</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1.864566652773817</v>
+        <v>1.495994623993719</v>
       </c>
       <c r="H155" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.118309234968699</v>
+        <v>1.089159548671955</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.157745646624932</v>
+        <v>1.171168102164085</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-0.1577456466249316</v>
+        <v>-0.1711681021640847</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.25</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>-0.1887865655471288</v>
+        <v>-0.2205882352941178</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>0.1982924719990118</v>
+        <v>0.3704687198874841</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>0</v>
@@ -65907,17 +65907,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>KNF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BlackLine, Inc.</t>
+          <t>Knife River Corporation</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -65926,34 +65926,34 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>187.822</v>
+        <v>938.587</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>5.856608916953285</v>
+        <v>1.278517601458362</v>
       </c>
       <c r="H156" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.213236048111025</v>
+        <v>1.069950017100908</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.284314730814701</v>
+        <v>1.093266689467878</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-0.2843147308147007</v>
+        <v>-0.09326668946787797</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>0.1648840410886372</v>
+        <v>-0.04260411680229781</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>-0.03967136846020192</v>
+        <v>-0.3209678112733748</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>0.09182967591919766</v>
+        <v>0.1257293774340067</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>0</v>
@@ -65962,53 +65962,53 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CTGG</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>QWEST CORPORATION</t>
+          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>1051</v>
+        <v>3161</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>1700</v>
+        <v>28000</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>1.617507136060894</v>
+        <v>8.857956342929453</v>
       </c>
       <c r="H157" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>0.9137930393824609</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>0.8850573858432812</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0.1149426141567188</v>
+        <v>-0.2101855938793955</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>-0.1904761904761905</v>
+        <v>0.07692307692307687</v>
       </c>
       <c r="M157" s="5" t="n">
-        <v>0.03679653679653683</v>
+        <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>-0.1399345335515548</v>
+        <v>0.04575379627485376</v>
       </c>
       <c r="O157" s="3" t="n">
         <v>0</v>
@@ -66017,53 +66017,53 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>CTGG</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MOTOROLA SOLUTIONS, INC.</t>
+          <t>QWEST CORPORATION</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>3133</v>
+        <v>1051</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>9500</v>
+        <v>1700</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>3.032237472071497</v>
+        <v>1.617507136060894</v>
       </c>
       <c r="H158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1.050872060091059</v>
+        <v>0.9137930393824609</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.067829413454745</v>
+        <v>0.8850573858432812</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-0.0678294134547448</v>
+        <v>0.1149426141567188</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>0.07954545454545459</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>0.01212972420837599</v>
+        <v>0.03679653679653683</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>0.1330922242314647</v>
+        <v>-0.1399345335515548</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>0</v>
@@ -66072,17 +66072,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -66091,34 +66091,34 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>176.1</v>
+        <v>9289</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>800</v>
+        <v>64000</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>4.542873367404884</v>
+        <v>6.889869738400258</v>
       </c>
       <c r="H159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1.480891850388013</v>
+        <v>1.085960275519686</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>1.641189133850684</v>
+        <v>1.114613700692915</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-0.6411891338506841</v>
+        <v>-0.1146137006929147</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.04918032786885251</v>
       </c>
       <c r="M159" s="5" t="n">
-        <v>0</v>
+        <v>-0.05426794799321644</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>0.1398058252427183</v>
+        <v>0.09346674514420239</v>
       </c>
       <c r="O159" s="3" t="n">
         <v>0</v>
@@ -66127,17 +66127,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>DOCUSIGN, INC.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -66146,34 +66146,34 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>9289</v>
+        <v>875.746</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>64000</v>
+        <v>2300</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>6.889869738400258</v>
+        <v>2.626332292696741</v>
       </c>
       <c r="H160" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>1.085960275519686</v>
+        <v>0.9997616187771211</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>1.114613700692915</v>
+        <v>0.9996821583694948</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-0.1146137006929147</v>
+        <v>0.000317841630505189</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>0.04918032786885251</v>
+        <v>0</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>-0.05426794799321644</v>
+        <v>0</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>0.09346674514420239</v>
+        <v>0.09381291872960995</v>
       </c>
       <c r="O160" s="3" t="n">
         <v>0</v>
@@ -66182,17 +66182,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>RYDER SYSTEM, INC.</t>
+          <t>TRIMBLE INC.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
+          <t>Measuring &amp; Controlling Devices, NEC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -66201,34 +66201,34 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>3347</v>
+        <v>972</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>3400</v>
+        <v>2000</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>1.015835076187631</v>
+        <v>2.05761316872428</v>
       </c>
       <c r="H161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.015760444815641</v>
+        <v>1.077335533099608</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.021013926420854</v>
+        <v>1.103114044132811</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-0.02101392642085442</v>
+        <v>-0.1031140441328109</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="M161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.04954531201003443</v>
+        <v>0.1099691675231242</v>
       </c>
       <c r="O161" s="3" t="n">
         <v>0</v>
@@ -66237,17 +66237,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RNG</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RingCentral, Inc.</t>
+          <t>RYDER SYSTEM, INC.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -66256,34 +66256,34 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>657.011</v>
+        <v>3347</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>4.109520236343075</v>
+        <v>1.015835076187631</v>
       </c>
       <c r="H162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>1.03880788389923</v>
+        <v>1.015760444815641</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>1.051743845198973</v>
+        <v>1.021013926420854</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-0.05174384519897313</v>
+        <v>-0.02101392642085442</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.0625</v>
       </c>
       <c r="M162" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>0.05901534176448009</v>
+        <v>0.04954531201003443</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>0</v>
@@ -66292,17 +66292,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Medpace Holdings, Inc.</t>
+          <t>LUMEN TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Services-Commercial Physical &amp; Biological Research</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -66311,34 +66311,34 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>707.331</v>
+        <v>2805</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>3500</v>
+        <v>5900</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>4.948178434141866</v>
+        <v>2.103386809269162</v>
       </c>
       <c r="H163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>0.9999078094493223</v>
+        <v>0.9914988391223929</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>0.9998770792657633</v>
+        <v>0.9886651188298572</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0.0001229207342366978</v>
+        <v>0.01133488117014281</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>0</v>
+        <v>-0.01666666666666672</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>-0.02941176470588225</v>
+        <v>0.01612021857923496</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>0.1724152219999304</v>
+        <v>-0.09282018111254853</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>0</v>
@@ -66347,17 +66347,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ciena Corp</t>
+          <t>Centrus Energy Corp.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Telephone &amp; Telegraph Apparatus</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -66366,34 +66366,34 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>1671.129</v>
+        <v>176.1</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>1.495994623993719</v>
+        <v>4.542873367404884</v>
       </c>
       <c r="H164" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.089159548671955</v>
+        <v>1.480891850388013</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>1.171168102164085</v>
+        <v>1.641189133850684</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-0.1711681021640847</v>
+        <v>-0.6411891338506841</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>-0.2205882352941178</v>
+        <v>0</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0.3704687198874841</v>
+        <v>0.1398058252427183</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>0</v>
@@ -66402,17 +66402,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUMEN TECHNOLOGIES, INC.</t>
+          <t>BlackLine, Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -66421,34 +66421,34 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>2805</v>
+        <v>187.822</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>5900</v>
+        <v>1100</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>2.103386809269162</v>
+        <v>5.856608916953285</v>
       </c>
       <c r="H165" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>0.9914988391223929</v>
+        <v>1.213236048111025</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>0.9886651188298572</v>
+        <v>1.284314730814701</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0.01133488117014281</v>
+        <v>-0.2843147308147007</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>-0.01666666666666672</v>
+        <v>0.1648840410886372</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>0.01612021857923496</v>
+        <v>-0.03967136846020192</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>-0.09282018111254853</v>
+        <v>0.09182967591919766</v>
       </c>
       <c r="O165" s="3" t="n">
         <v>0</v>
@@ -66457,17 +66457,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -66476,34 +66476,34 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>3161</v>
+        <v>911.74</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>28000</v>
+        <v>1700</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>8.857956342929453</v>
+        <v>1.864566652773817</v>
       </c>
       <c r="H166" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>1.118309234968699</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>1.157745646624932</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-0.2101855938793955</v>
+        <v>-0.1577456466249316</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>0</v>
+        <v>-0.1887865655471288</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>0.04575379627485376</v>
+        <v>0.1982924719990118</v>
       </c>
       <c r="O166" s="3" t="n">
         <v>0</v>
@@ -66512,17 +66512,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>COLD</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TRIMBLE INC.</t>
+          <t>AMERICOLD REALTY TRUST, INC.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Measuring &amp; Controlling Devices, NEC</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -66531,34 +66531,34 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>972</v>
+        <v>662.89</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>2.05761316872428</v>
+        <v>2.564528051411245</v>
       </c>
       <c r="H167" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1.077335533099608</v>
+        <v>1.119072189499421</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>1.103114044132811</v>
+        <v>1.158762919332561</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-0.1031140441328109</v>
+        <v>-0.1587629193325606</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>0.1764705882352942</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="M167" s="5" t="n">
-        <v>0</v>
+        <v>-0.09340659340659352</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>0.1099691675231242</v>
+        <v>0.01865852833969517</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>0</v>
@@ -66567,17 +66567,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KNF</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Knife River Corporation</t>
+          <t>MOTOROLA SOLUTIONS, INC.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Radio &amp; Tv Broadcasting &amp; Communications Equipment</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -66586,34 +66586,34 @@
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>938.587</v>
+        <v>3133</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1200</v>
+        <v>9500</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1.278517601458362</v>
+        <v>3.032237472071497</v>
       </c>
       <c r="H168" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>1.069950017100908</v>
+        <v>1.050872060091059</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>1.093266689467878</v>
+        <v>1.067829413454745</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-0.09326668946787797</v>
+        <v>-0.0678294134547448</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>-0.04260411680229781</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>-0.3209678112733748</v>
+        <v>0.01212972420837599</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>0.1257293774340067</v>
+        <v>0.1330922242314647</v>
       </c>
       <c r="O168" s="3" t="n">
         <v>0</v>
@@ -66622,17 +66622,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>RNG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DOCUSIGN, INC.</t>
+          <t>RingCentral, Inc.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -66641,34 +66641,34 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>875.746</v>
+        <v>657.011</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>2.626332292696741</v>
+        <v>4.109520236343075</v>
       </c>
       <c r="H169" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>0.9997616187771211</v>
+        <v>1.03880788389923</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>0.9996821583694948</v>
+        <v>1.051743845198973</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0.000317841630505189</v>
+        <v>-0.05174384519897313</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>0</v>
+        <v>0.03846153846153855</v>
       </c>
       <c r="M169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>0.09381291872960995</v>
+        <v>0.05901534176448009</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>0</v>
@@ -66677,17 +66677,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>COLD</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AMERICOLD REALTY TRUST, INC.</t>
+          <t>Medpace Holdings, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Services-Commercial Physical &amp; Biological Research</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -66696,34 +66696,34 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>662.89</v>
+        <v>707.331</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>1700</v>
+        <v>3500</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>2.564528051411245</v>
+        <v>4.948178434141866</v>
       </c>
       <c r="H170" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>1.119072189499421</v>
+        <v>0.9999078094493223</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>1.158762919332561</v>
+        <v>0.9998770792657633</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-0.1587629193325606</v>
+        <v>0.0001229207342366978</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>0.2142857142857142</v>
+        <v>0</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>-0.09340659340659352</v>
+        <v>-0.02941176470588225</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>0.01865852833969517</v>
+        <v>0.1724152219999304</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>0</v>

--- a/results/market_bookings_screen.xlsx
+++ b/results/market_bookings_screen.xlsx
@@ -1140,12 +1140,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUNOCOCORP LLC</t>
+          <t>SUNOCO LP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>1.003716950697805</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1177,12 +1177,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>SUNC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SUNOCO LP</t>
+          <t>SUNOCOCORP LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1203,7 +1203,7 @@
         <v>1.003716950697805</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>ZAYO GROUP HOLDINGS, INC.</t>
+          <t>ZAYO GROUP LLC</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10474,7 +10474,7 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>ZAYO GROUP LLC</t>
+          <t>ZAYO GROUP HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11179,33 +11179,33 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>GBTG</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Moderna, Inc.</t>
+          <t>Global Business Travel Group, Inc.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2020Q4</t>
+          <t>2023Q3</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E300" s="3" t="n">
-        <v>87.22499999999999</v>
+        <v>5</v>
       </c>
       <c r="F300" s="4" t="n">
-        <v>0.1527583187390543</v>
+        <v>0.008756567425569177</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>0.9689667250437828</v>
+        <v>0.9947460595446584</v>
       </c>
       <c r="H300" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -11216,33 +11216,33 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>GBTG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Global Business Travel Group, Inc.</t>
+          <t>Moderna, Inc.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2023Q3</t>
+          <t>2020Q4</t>
         </is>
       </c>
       <c r="D301" s="3" t="n">
         <v>571</v>
       </c>
       <c r="E301" s="3" t="n">
-        <v>5</v>
+        <v>87.22499999999999</v>
       </c>
       <c r="F301" s="4" t="n">
-        <v>0.008756567425569177</v>
+        <v>0.1527583187390543</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>0.9947460595446584</v>
+        <v>0.9689667250437828</v>
       </c>
       <c r="H301" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -13356,71 +13356,71 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>MTB</t>
-        </is>
-      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>M&amp;T BANK CORPORATION</t>
+          <t>AVAYA HOLDINGS CORP.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2022Q4</t>
         </is>
       </c>
       <c r="D362" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E362" s="3" t="n">
-        <v>73</v>
+        <v>1920</v>
       </c>
       <c r="F362" s="4" t="n">
-        <v>0.1746411483253588</v>
+        <v>4.593301435406699</v>
       </c>
       <c r="G362" s="4" t="n">
-        <v>0.9952153110047847</v>
+        <v>0.8038277511961722</v>
       </c>
       <c r="H362" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>failed a data-quality check</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MTB</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>AVAYA HOLDINGS CORP.</t>
+          <t>M&amp;T BANK CORPORATION</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2022Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D363" s="3" t="n">
         <v>418</v>
       </c>
       <c r="E363" s="3" t="n">
-        <v>1920</v>
+        <v>73</v>
       </c>
       <c r="F363" s="4" t="n">
-        <v>4.593301435406699</v>
+        <v>0.1746411483253588</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>0.8038277511961722</v>
+        <v>0.9952153110047847</v>
       </c>
       <c r="H363" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>failed a data-quality check</t>
         </is>
       </c>
     </row>
@@ -21148,71 +21148,71 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>COHU</t>
-        </is>
-      </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>COHU, INC.</t>
+          <t>HOLLY ENERGY PARTNERS LP</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2022Q3</t>
         </is>
       </c>
       <c r="D588" s="3" t="n">
         <v>149.002</v>
       </c>
       <c r="E588" s="3" t="n">
-        <v>4.8</v>
+        <v>1557</v>
       </c>
       <c r="F588" s="4" t="n">
-        <v>0.03221433269352089</v>
+        <v>10.44952416746084</v>
       </c>
       <c r="G588" s="4" t="n">
-        <v>0.999328868068885</v>
+        <v>0.3892699426853331</v>
       </c>
       <c r="H588" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
+          <t>no recent filing</t>
         </is>
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>COHU</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>HOLLY ENERGY PARTNERS LP</t>
+          <t>COHU, INC.</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2022Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="D589" s="3" t="n">
         <v>149.002</v>
       </c>
       <c r="E589" s="3" t="n">
-        <v>1557</v>
+        <v>4.8</v>
       </c>
       <c r="F589" s="4" t="n">
-        <v>10.44952416746084</v>
+        <v>0.03221433269352089</v>
       </c>
       <c r="G589" s="4" t="n">
-        <v>0.3892699426853331</v>
+        <v>0.999328868068885</v>
       </c>
       <c r="H589" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>no recent filing</t>
+          <t>RPO cover under 1 quarter - book-to-bill not meaningful</t>
         </is>
       </c>
     </row>
@@ -38654,7 +38654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -38671,7 +38671,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>The 132 names worth running the deep segment-level pass on. Tier 2 costs about 335 SEC requests and 47MB per name, so this list is what keeps it to a few hours rather than a few days.</t>
+          <t>The 131 names worth running the deep segment-level pass on. Tier 2 costs about 335 SEC requests and 47MB per name, so this list is what keeps it to a few hours rather than a few days.</t>
         </is>
       </c>
     </row>
@@ -43002,315 +43002,280 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Services-Employment Agencies</t>
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>1.053424100167196</v>
+        <v>1.052574997842071</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>-0.02025115451579329</v>
+        <v>-0.0105698676487862</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.1515151515151516</v>
+        <v>0.1725386313465784</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>-0.04203323558162264</v>
+        <v>0.05909288988527273</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>18718.144</v>
+        <v>764.622</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>2.030115806353451</v>
+        <v>1.736675115285723</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>SPOK HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Services-Employment Agencies</t>
+          <t>Radiotelephone Communications</t>
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>1.052574997842071</v>
+        <v>1.051412413241553</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.0105698676487862</v>
+        <v>0.1494077634480548</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1725386313465784</v>
+        <v>-0.1242331288343559</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.05909288988527273</v>
+        <v>0.0007668711656442229</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>764.622</v>
+        <v>35.011</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>1.736675115285723</v>
+        <v>1.630915997829254</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SPOK</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPOK HOLDINGS, INC.</t>
+          <t>KBR, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Radiotelephone Communications</t>
+          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
         </is>
       </c>
       <c r="D131" s="4" t="n">
-        <v>1.051412413241553</v>
+        <v>1.050403225806452</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>0.1494077634480548</v>
+        <v>-0.03528077442093025</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>-0.1242331288343559</v>
+        <v>0.04580152671755733</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.0007668711656442229</v>
+        <v>0.06029428034074569</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>35.011</v>
+        <v>1984</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>1.630915997829254</v>
+        <v>6.905241935483871</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KBR, Inc.</t>
+          <t>QUANTUM CORP /DE/</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
+          <t>Computer Storage Devices</t>
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>1.050403225806452</v>
+        <v>1.03305570337735</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.03528077442093025</v>
+        <v>0.03553398255919094</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.04580152671755733</v>
+        <v>0.3255882705445248</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.06029428034074569</v>
+        <v>0.1429375529105072</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>1984</v>
+        <v>80.803</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>6.905241935483871</v>
+        <v>2.05319109439006</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>SHIM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>QUANTUM CORP /DE/</t>
+          <t>Shimmick Corporation</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Computer Storage Devices</t>
+          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
         </is>
       </c>
       <c r="D133" s="4" t="n">
-        <v>1.03305570337735</v>
+        <v>0.7655136189690103</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>0.03553398255919094</v>
+        <v>-1.242397456074783</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.3255882705445248</v>
+        <v>0.4744645799011533</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.1429375529105072</v>
+        <v>0.1449848111150263</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>80.803</v>
+        <v>106.616</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2.05319109439006</v>
+        <v>8.394612440909432</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHIM</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shimmick Corporation</t>
+          <t>SMART SAND, INC.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.7655136189690103</v>
+        <v>0.7165406345067362</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-1.242397456074783</v>
+        <v>-0.9228557327858946</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.4744645799011533</v>
+        <v>1.921212490294292</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.1449848111150263</v>
+        <v>1.03139289724118</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>106.616</v>
+        <v>115.05</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8.394612440909432</v>
+        <v>1.6677444589309</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>AMWL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SMART SAND, INC.</t>
+          <t>American Well Corporation</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>0.7165406345067362</v>
+        <v>0.5792153396864433</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>-0.9228557327858946</v>
+        <v>-0.5492391602924506</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>1.921212490294292</v>
+        <v>-0.004437887282384034</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>1.03139289724118</v>
+        <v>0.1405964722779424</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>115.05</v>
+        <v>52.048</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>1.6677444589309</v>
+        <v>1.620600215185982</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMWL</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>American Well Corporation</t>
+          <t>New Fortress Energy Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Natural Gas Distribution</t>
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>0.5792153396864433</v>
+        <v>0.5764059110021702</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.5492391602924506</v>
+        <v>-1.857647551449775</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.004437887282384034</v>
+        <v>0.1899874222194355</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.1405964722779424</v>
+        <v>0.3469700812886806</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>52.048</v>
+        <v>312.502</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1.620600215185982</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>NFE</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>New Fortress Energy Inc.</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Natural Gas Distribution</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>0.5764059110021702</v>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>-1.857647551449775</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>0.1899874222194355</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>0.3469700812886806</v>
-      </c>
-      <c r="H137" s="3" t="n">
-        <v>312.502</v>
-      </c>
-      <c r="I137" s="4" t="n">
         <v>32.55178526857428</v>
       </c>
     </row>
@@ -43318,7 +43283,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D137">
+  <conditionalFormatting sqref="D6:D136">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -43330,7 +43295,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F137">
+  <conditionalFormatting sqref="F6:F136">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -50807,7 +50772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -53747,11 +53712,66 @@
         <v>-37.30000000000007</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Accenture plc</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Services-Business Services, NEC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>18679.11</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>37000</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1.980822426764444</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.9464642587360961</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>1.04102096617605</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>1.072539868656035</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>-0.1260756099199387</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0.08823529411764697</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>-0.06327985739750464</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.0615386451439115</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>-1000</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H57">
+  <conditionalFormatting sqref="H6:H58">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -53763,7 +53783,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K57">
+  <conditionalFormatting sqref="K6:K58">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -53775,7 +53795,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L57">
+  <conditionalFormatting sqref="L6:L58">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -53787,7 +53807,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M57">
+  <conditionalFormatting sqref="M6:M58">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="percentile" val="5"/>
@@ -56557,10 +56577,10 @@
         <v>0.8973436257255196</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1289585557241044</v>
+        <v>0.09967320261437906</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.290129536414548</v>
+        <v>2.265482846620044</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0.125</v>
@@ -64431,17 +64451,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Services-Business Services, NEC</t>
+          <t>Services-Employment Agencies</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -64450,53 +64470,53 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>18718.144</v>
+        <v>764.622</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>38000</v>
+        <v>1327.9</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>2.030115806353451</v>
+        <v>1.736675115285723</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>1.053424100167196</v>
+        <v>1.052574997842071</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>1.068612466054041</v>
+        <v>1.091850185171579</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>1.073675254682989</v>
+        <v>1.063144865490857</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-0.02025115451579329</v>
+        <v>-0.0105698676487862</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.1515151515151516</v>
+        <v>0.1725386313465784</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>-0.04203323558162264</v>
+        <v>0.05909288988527273</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>0.05585966865395187</v>
+        <v>0.06858986811414547</v>
       </c>
       <c r="O129" s="3" t="n">
-        <v>1000</v>
+        <v>40.20000000000005</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>SPOK HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Services-Employment Agencies</t>
+          <t>Radiotelephone Communications</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -64505,53 +64525,53 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>764.622</v>
+        <v>35.011</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1327.9</v>
+        <v>57.1</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1.736675115285723</v>
+        <v>1.630915997829254</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.052574997842071</v>
+        <v>1.051412413241553</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>1.091850185171579</v>
+        <v>0.9393565906555117</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>1.063144865490857</v>
+        <v>0.9020046497934979</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-0.0105698676487862</v>
+        <v>0.1494077634480548</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>0.1725386313465784</v>
+        <v>-0.1242331288343559</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>0.05909288988527273</v>
+        <v>0.0007668711656442229</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>0.06858986811414547</v>
+        <v>-0.01891498066468633</v>
       </c>
       <c r="O130" s="3" t="n">
-        <v>40.20000000000005</v>
+        <v>1.800000000000004</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SPOK</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPOK HOLDINGS, INC.</t>
+          <t>KBR, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Radiotelephone Communications</t>
+          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -64560,53 +64580,53 @@
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>35.011</v>
+        <v>1984</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>57.1</v>
+        <v>13700</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1.630915997829254</v>
+        <v>6.905241935483871</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>1.051412413241553</v>
+        <v>1.050403225806452</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>0.9393565906555117</v>
+        <v>1.076863806622149</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>0.9020046497934979</v>
+        <v>1.085684000227382</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0.1494077634480548</v>
+        <v>-0.03528077442093025</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>-0.1242331288343559</v>
+        <v>0.04580152671755733</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>0.0007668711656442229</v>
+        <v>0.06029428034074569</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>-0.01891498066468633</v>
+        <v>0.01639344262295084</v>
       </c>
       <c r="O131" s="3" t="n">
-        <v>1.800000000000004</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KBR, Inc.</t>
+          <t>TENABLE HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Heavy Construction Other Than Bldg Const - Contractors</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -64615,53 +64635,53 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>1984</v>
+        <v>268.508</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>13700</v>
+        <v>1026.11</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>6.905241935483871</v>
+        <v>3.821524870767351</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>1.050403225806452</v>
+        <v>1.048065606983777</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>1.076863806622149</v>
+        <v>1.132550977238927</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>1.085684000227382</v>
+        <v>1.160712767323977</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-0.03528077442093025</v>
+        <v>-0.1126471603402004</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0.04580152671755733</v>
+        <v>0.1540438377178923</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.06029428034074569</v>
+        <v>0.005605478758646365</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>0.01639344262295084</v>
+        <v>0.08578014112699406</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>100</v>
+        <v>12.90599999999995</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TENABLE HOLDINGS, INC.</t>
+          <t>RBC BEARINGS INCORPORATED</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Ball &amp; Roller Bearings</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -64670,53 +64690,53 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>268.508</v>
+        <v>519.5</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1026.11</v>
+        <v>1292</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>3.821524870767351</v>
+        <v>2.487006737247353</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>1.048065606983777</v>
+        <v>1.047738209817132</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>1.132550977238927</v>
+        <v>1.369054001885819</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>1.160712767323977</v>
+        <v>1.407651968644023</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-0.1126471603402004</v>
+        <v>-0.3599137588268913</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>0.1540438377178923</v>
+        <v>1.105949470252649</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>0.005605478758646365</v>
+        <v>-0.2311954947049313</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>0.08578014112699406</v>
+        <v>0.1915137614678899</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>12.90599999999995</v>
+        <v>24.79999999999995</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RBC BEARINGS INCORPORATED</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ball &amp; Roller Bearings</t>
+          <t>Services-Computer Integrated Systems Design</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -64725,53 +64745,53 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>519.5</v>
+        <v>1298</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>1292</v>
+        <v>3510.9</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>2.487006737247353</v>
+        <v>2.704853620955316</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>1.047738209817132</v>
+        <v>1.046456086286595</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>1.369054001885819</v>
+        <v>1.033986910665643</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>1.407651968644023</v>
+        <v>1.029830518791992</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-0.3599137588268913</v>
+        <v>0.01662556749460253</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>1.105949470252649</v>
+        <v>0.05195505617977525</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>-0.2311954947049313</v>
+        <v>-0.00501976462522391</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.1915137614678899</v>
+        <v>0.06603153745072277</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>24.79999999999995</v>
+        <v>60.30000000000018</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>SPROUT SOCIAL, INC.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Services-Computer Integrated Systems Design</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -64780,53 +64800,50 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>1298</v>
+        <v>123.847</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>3510.9</v>
+        <v>400.8</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>2.704853620955316</v>
+        <v>3.236251180892553</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>1.046456086286595</v>
-      </c>
-      <c r="I135" s="4" t="n">
-        <v>1.033986910665643</v>
+        <v>1.044409634468336</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>1.029830518791992</v>
+        <v>1.043023063866542</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0.01662556749460253</v>
+        <v>0.001386570601793702</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.05195505617977525</v>
+        <v>0.1550432276657061</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>-0.00501976462522391</v>
+        <v>0.05759736425648887</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>0.06603153745072277</v>
+        <v>0.1079729463758521</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>60.30000000000018</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SPROUT SOCIAL, INC.</t>
+          <t>ARM HOLDINGS PLC /UK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Semiconductors &amp; Related Devices</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -64835,50 +64852,53 @@
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>123.847</v>
+        <v>1289</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>400.8</v>
+        <v>2122.6</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>3.236251180892553</v>
+        <v>1.646702870442203</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>1.044409634468336</v>
+        <v>1.039720713731575</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>0.9910106853674948</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>1.043023063866542</v>
+        <v>0.9799546829745388</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0.001386570601793702</v>
+        <v>0.0597660307570359</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>0.1550432276657061</v>
+        <v>-0.04918473391865263</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.05759736425648887</v>
+        <v>0.02005813285285929</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>0.1079729463758521</v>
+        <v>0.2241215574548907</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>5.5</v>
+        <v>51.19999999999982</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ARM HOLDINGS PLC /UK</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Related Devices</t>
+          <t>Motor Vehicles &amp; Passenger Car Bodies</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -64887,53 +64907,53 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>1289</v>
+        <v>2915.1</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>2122.6</v>
+        <v>12300</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1.646702870442203</v>
+        <v>4.219409282700422</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>1.039720713731575</v>
+        <v>1.034304140509759</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>0.9910106853674948</v>
+        <v>0.9777053349357657</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>0.9799546829745388</v>
+        <v>0.9588390664111012</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0.0597660307570359</v>
+        <v>0.07546507409865832</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>-0.04918473391865263</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>0.02005813285285929</v>
+        <v>-0.00706417546709992</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>0.2241215574548907</v>
+        <v>0.06698144284616236</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>51.19999999999982</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>PACB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>Pacific Biosciences of California, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Motor Vehicles &amp; Passenger Car Bodies</t>
+          <t>Laboratory Analytical Instruments</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -64942,53 +64962,53 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>2915.1</v>
+        <v>39.007</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>12300</v>
+        <v>47.9</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>4.219409282700422</v>
+        <v>1.227984720691158</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>1.034304140509759</v>
+        <v>1.033327351501013</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0.9777053349357657</v>
+        <v>0.9192945924875482</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>0.9588390664111012</v>
+        <v>0.8905824979026494</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0.07546507409865832</v>
+        <v>0.1427448535983632</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>-0.01600000000000001</v>
+        <v>-0.1537102473498234</v>
       </c>
       <c r="M138" s="5" t="n">
-        <v>-0.00706417546709992</v>
+        <v>0.05242263169617323</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>0.06698144284616236</v>
+        <v>-0.01908665694311729</v>
       </c>
       <c r="O138" s="3" t="n">
-        <v>100</v>
+        <v>1.299999999999997</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pacific Biosciences of California, Inc.</t>
+          <t>QUANTUM CORP /DE/</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Laboratory Analytical Instruments</t>
+          <t>Computer Storage Devices</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -64997,53 +65017,53 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>39.007</v>
+        <v>80.803</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>47.9</v>
+        <v>165.904</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>1.227984720691158</v>
+        <v>2.05319109439006</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>1.033327351501013</v>
+        <v>1.03305570337735</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0.9192945924875482</v>
+        <v>1.075262955028388</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0.8905824979026494</v>
+        <v>0.9975217208181588</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0.1427448535983632</v>
+        <v>0.03553398255919094</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>-0.1537102473498234</v>
+        <v>0.3255882705445248</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>0.05242263169617323</v>
+        <v>0.1429375529105072</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>-0.01908665694311729</v>
+        <v>0.2569299692001368</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>1.299999999999997</v>
+        <v>2.670999999999992</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>QUANTUM CORP /DE/</t>
+          <t>DIGI INTERNATIONAL INC.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Computer Storage Devices</t>
+          <t>Computer Communications Equipment</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -65052,53 +65072,53 @@
         </is>
       </c>
       <c r="E140" s="3" t="n">
-        <v>80.803</v>
+        <v>138.67</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>165.904</v>
+        <v>240.1</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>2.05319109439006</v>
+        <v>1.731448763250883</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>1.03305570337735</v>
+        <v>1.026682050912238</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>1.075262955028388</v>
+        <v>1.094738967573207</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>0.9975217208181588</v>
+        <v>1.079954244895917</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0.03553398255919094</v>
+        <v>-0.05327219398367933</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>0.3255882705445248</v>
+        <v>0.5110132158590308</v>
       </c>
       <c r="M140" s="5" t="n">
-        <v>0.1429375529105072</v>
+        <v>0.04086396212768761</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>0.2569299692001368</v>
+        <v>0.2897855163048533</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>2.670999999999992</v>
+        <v>3.699999999999989</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DIGI INTERNATIONAL INC.</t>
+          <t>THERMO FISHER SCIENTIFIC INC.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Computer Communications Equipment</t>
+          <t>Measuring &amp; Controlling Devices, NEC</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -65107,163 +65127,163 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>138.67</v>
+        <v>11994</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>240.1</v>
+        <v>29700</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1.731448763250883</v>
+        <v>2.47623811905953</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>1.026682050912238</v>
+        <v>1.024178756044689</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>1.094738967573207</v>
+        <v>1.101692952952612</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>1.079954244895917</v>
+        <v>1.127531018588587</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-0.05327219398367933</v>
+        <v>-0.1033522625438976</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>0.5110132158590308</v>
+        <v>0.1861022364217253</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>0.04086396212768761</v>
+        <v>-0.01234927132073604</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>0.2897855163048533</v>
+        <v>0.1049286043298019</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>3.699999999999989</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>THERMO FISHER SCIENTIFIC INC.</t>
+          <t>MICROSOFT CORPORATION</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Measuring &amp; Controlling Devices, NEC</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E142" s="3" t="n">
-        <v>11994</v>
+        <v>82886</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>29700</v>
+        <v>633000</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>2.47623811905953</v>
+        <v>7.636995391260285</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>1.024178756044689</v>
+        <v>1.02412952730256</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>1.101692952952612</v>
+        <v>2.062374493232325</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>1.127531018588587</v>
+        <v>2.135207443783799</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-0.1033522625438976</v>
+        <v>-1.111077916481239</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0.1861022364217253</v>
+        <v>0.97196261682243</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>-0.01234927132073604</v>
+        <v>-0.103695277914412</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>0.1049286043298019</v>
+        <v>0.182970342248737</v>
       </c>
       <c r="O142" s="3" t="n">
-        <v>290</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MICROSOFT CORPORATION</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Services-Consumer Credit Reporting, Collection Agencies</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>82886</v>
+        <v>4146</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>633000</v>
+        <v>5800</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>7.636995391260285</v>
+        <v>1.398938736131211</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>1.02412952730256</v>
+        <v>1.024119633381573</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>2.062374493232325</v>
+        <v>1.057883029107971</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>2.135207443783799</v>
+        <v>1.069137494350105</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1.111077916481239</v>
+        <v>-0.04501786096853211</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>0.97196261682243</v>
+        <v>0.1836734693877551</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>-0.103695277914412</v>
+        <v>0.02040816326530615</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>0.182970342248737</v>
+        <v>0.1041278295605859</v>
       </c>
       <c r="O143" s="3" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MTZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>MasTec, Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Services-Consumer Credit Reporting, Collection Agencies</t>
+          <t>Water, Sewer, Pipeline, Comm &amp; Power Line Construction</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -65272,34 +65292,34 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>4146</v>
+        <v>4373.554</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>5800</v>
+        <v>16300</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>1.398938736131211</v>
+        <v>3.726946094640652</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>1.024119633381573</v>
+        <v>1.02286469996712</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>1.057883029107971</v>
+        <v>1.313113238038031</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>1.069137494350105</v>
+        <v>1.409862750728334</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-0.04501786096853211</v>
+        <v>-0.3869980507612134</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>0.1836734693877551</v>
+        <v>0.4298245614035088</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>0.02040816326530615</v>
+        <v>-0.04290271132376389</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>0.1041278295605859</v>
+        <v>0.2338273565783331</v>
       </c>
       <c r="O144" s="3" t="n">
         <v>100</v>
@@ -65308,17 +65328,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MTZ</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MasTec, Inc.</t>
+          <t>EMERSON ELECTRIC CO.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Water, Sewer, Pipeline, Comm &amp; Power Line Construction</t>
+          <t>Electronic &amp; Other Electrical Equipment (No Computer Equip)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -65327,34 +65347,34 @@
         </is>
       </c>
       <c r="E145" s="3" t="n">
-        <v>4373.554</v>
+        <v>4873</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>16300</v>
+        <v>9600</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>3.726946094640652</v>
+        <v>1.970038990355018</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>1.02286469996712</v>
+        <v>1.020521239482865</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>1.313113238038031</v>
+        <v>1.040636972023517</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>1.409862750728334</v>
+        <v>1.047342216203735</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-0.3869980507612134</v>
+        <v>-0.02682097672087025</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>0.4298245614035088</v>
+        <v>0.0786516853932584</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>-0.04290271132376389</v>
+        <v>-0.0008937691521961888</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>0.2338273565783331</v>
+        <v>0.0702833296727432</v>
       </c>
       <c r="O145" s="3" t="n">
         <v>100</v>
@@ -65363,17 +65383,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>TGLS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EMERSON ELECTRIC CO.</t>
+          <t>TECNOGLASS HOLDINGS INC.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Electronic &amp; Other Electrical Equipment (No Computer Equip)</t>
+          <t>Flat Glass</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -65382,53 +65402,53 @@
         </is>
       </c>
       <c r="E146" s="3" t="n">
-        <v>4873</v>
+        <v>295.291</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>9600</v>
+        <v>884.2</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1.970038990355018</v>
+        <v>2.994334402335324</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>1.020521239482865</v>
+        <v>1.019980290628567</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>1.040636972023517</v>
+        <v>1.060241439146608</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>1.047342216203735</v>
+        <v>1.073661821985955</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-0.02682097672087025</v>
+        <v>-0.05368153135738818</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>0.0786516853932584</v>
+        <v>0.07829268292682934</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>-0.0008937691521961888</v>
+        <v>-0.05499763965381566</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>0.0702833296727432</v>
+        <v>0.1555297285028918</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>100</v>
+        <v>5.900000000000091</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TGLS</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TECNOGLASS HOLDINGS INC.</t>
+          <t>PEGASYSTEMS INC.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Flat Glass</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -65437,53 +65457,53 @@
         </is>
       </c>
       <c r="E147" s="3" t="n">
-        <v>295.291</v>
+        <v>420.716</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>884.2</v>
+        <v>2018.631</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>2.994334402335324</v>
+        <v>4.798084693712624</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>1.019980290628567</v>
+        <v>1.01876325121935</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>1.060241439146608</v>
+        <v>1.07329004664543</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>1.073661821985955</v>
+        <v>1.091465645120791</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-0.05368153135738818</v>
+        <v>-0.07270239390144084</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>0.07829268292682934</v>
+        <v>0.09987419149373222</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>-0.05499763965381566</v>
+        <v>-0.06341083210188447</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>0.1555297285028918</v>
+        <v>0.09415570905459392</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>5.900000000000091</v>
+        <v>7.894000000000005</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>ASAN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEGASYSTEMS INC.</t>
+          <t>Asana, Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -65492,163 +65512,157 @@
         </is>
       </c>
       <c r="E148" s="3" t="n">
-        <v>420.716</v>
+        <v>216.429</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>2018.631</v>
+        <v>522</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>4.798084693712624</v>
+        <v>2.411876412125916</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>1.01876325121935</v>
+        <v>1.018019766297492</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>1.07329004664543</v>
+        <v>1.017444627353924</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>1.091465645120791</v>
+        <v>1.017252914372734</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-0.07270239390144084</v>
+        <v>0.0007668519247581163</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>0.09987419149373222</v>
+        <v>0.02897693672383195</v>
       </c>
       <c r="M148" s="5" t="n">
-        <v>-0.06341083210188447</v>
+        <v>-0.2025419603524696</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>0.09415570905459392</v>
+        <v>0.09898139497095504</v>
       </c>
       <c r="O148" s="3" t="n">
-        <v>7.894000000000005</v>
+        <v>3.899999999999977</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ASAN</t>
+          <t>EXTR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Asana, Inc.</t>
+          <t>EXTREME NETWORKS, INC.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Computer Communications Equipment</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
-        <v>216.429</v>
+        <v>316.874</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>522</v>
+        <v>647.1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>2.411876412125916</v>
+        <v>2.042136622127407</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>1.018019766297492</v>
+        <v>1.013254479698555</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>1.017444627353924</v>
+        <v>1.031430707987134</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>1.017252914372734</v>
+        <v>1.026075247630095</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0.0007668519247581163</v>
+        <v>-0.01282076793153997</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>0.02897693672383195</v>
+        <v>0.0992016307117376</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>-0.2025419603524696</v>
+        <v>0.008616388981457668</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>0.09898139497095504</v>
+        <v>0.1137730444104674</v>
       </c>
       <c r="O149" s="3" t="n">
-        <v>3.899999999999977</v>
+        <v>4.200000000000045</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EXTR</t>
+          <t>XZO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXTREME NETWORKS, INC.</t>
+          <t>Exzeo Group, Inc.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Computer Communications Equipment</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>316.874</v>
+        <v>57.787</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>647.1</v>
+        <v>75.36799999999999</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2.042136622127407</v>
+        <v>1.304237977399761</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>1.013254479698555</v>
+        <v>1.013013307491304</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>1.031430707987134</v>
+        <v>0.9886124674315936</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>1.026075247630095</v>
+        <v>0.9764120474017383</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-0.01282076793153997</v>
-      </c>
-      <c r="L150" s="5" t="n">
-        <v>0.0992016307117376</v>
-      </c>
-      <c r="M150" s="5" t="n">
-        <v>0.008616388981457668</v>
+        <v>0.03660126008956588</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>0.1137730444104674</v>
+        <v>0.0302365798434685</v>
       </c>
       <c r="O150" s="3" t="n">
-        <v>4.200000000000045</v>
+        <v>0.7519999999999953</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>LINE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Exzeo Group, Inc.</t>
+          <t>Lineage, Inc.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -65657,47 +65671,53 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>57.787</v>
+        <v>1361</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>75.36799999999999</v>
+        <v>1736</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>1.304237977399761</v>
+        <v>1.275532696546657</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>1.013013307491304</v>
+        <v>1.00661278471712</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>0.9886124674315936</v>
+        <v>1.100420689211619</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>0.9764120474017383</v>
+        <v>1.131689990709785</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0.03660126008956588</v>
+        <v>-0.1250772059926653</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>0.4430590191188695</v>
+      </c>
+      <c r="M151" s="5" t="n">
+        <v>-0.09890526659541621</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>0.0302365798434685</v>
+        <v>0.008148148148148238</v>
       </c>
       <c r="O151" s="3" t="n">
-        <v>0.7519999999999953</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>LINE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lineage, Inc.</t>
+          <t>AT&amp;T INC.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -65706,163 +65726,163 @@
         </is>
       </c>
       <c r="E152" s="3" t="n">
-        <v>1361</v>
+        <v>31558</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>1736</v>
+        <v>44582</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>1.275532696546657</v>
+        <v>1.412700424614995</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1.00661278471712</v>
+        <v>1.00602066037138</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1.100420689211619</v>
+        <v>1.019507606259529</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>1.131689990709785</v>
+        <v>1.024003254888912</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-0.1250772059926653</v>
+        <v>-0.0179825945175327</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>0.4430590191188695</v>
+        <v>0.06127404303942097</v>
       </c>
       <c r="M152" s="5" t="n">
-        <v>-0.09890526659541621</v>
+        <v>-0.003665383612851958</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>0.008148148148148238</v>
+        <v>0.02304924303822098</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>AT&amp;T INC.</t>
+          <t>CISCO SYSTEMS, INC.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Computer Communications Equipment</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>31558</v>
+        <v>15841</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>44582</v>
+        <v>43462</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1.412700424614995</v>
+        <v>2.743639921722114</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1.00602066037138</v>
+        <v>1.003535130357932</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>1.019507606259529</v>
+        <v>0.997971540543224</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>1.024003254888912</v>
+        <v>1.006193121351423</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-0.0179825945175327</v>
+        <v>-0.002657990993490955</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>0.06127404303942097</v>
+        <v>0.04307965536275704</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>-0.003665383612851958</v>
+        <v>-0.008728040672912218</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>0.02304924303822098</v>
+        <v>0.1195844229274154</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>190</v>
+        <v>56</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CISCO SYSTEMS, INC.</t>
+          <t>DOCUSIGN, INC.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Computer Communications Equipment</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>15841</v>
+        <v>875.746</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>43462</v>
+        <v>2300</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>2.743639921722114</v>
+        <v>2.626332292696741</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>1.003535130357932</v>
+        <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0.997971540543224</v>
+        <v>0.9997616187771211</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>1.006193121351423</v>
+        <v>0.9996821583694948</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-0.002657990993490955</v>
+        <v>0.000317841630505189</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>0.04307965536275704</v>
+        <v>0</v>
       </c>
       <c r="M154" s="5" t="n">
-        <v>-0.008728040672912218</v>
+        <v>0</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>0.1195844229274154</v>
+        <v>0.09381291872960995</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ciena Corp</t>
+          <t>LUMEN TECHNOLOGIES, INC.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Telephone &amp; Telegraph Apparatus</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -65871,34 +65891,34 @@
         </is>
       </c>
       <c r="E155" s="3" t="n">
-        <v>1671.129</v>
+        <v>2805</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>2500</v>
+        <v>5900</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>1.495994623993719</v>
+        <v>2.103386809269162</v>
       </c>
       <c r="H155" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.089159548671955</v>
+        <v>0.9914988391223929</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>1.171168102164085</v>
+        <v>0.9886651188298572</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-0.1711681021640847</v>
+        <v>0.01133488117014281</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0.25</v>
+        <v>-0.01666666666666672</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>-0.2205882352941178</v>
+        <v>0.01612021857923496</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>0.3704687198874841</v>
+        <v>-0.09282018111254853</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>0</v>
@@ -65907,17 +65927,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KNF</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Knife River Corporation</t>
+          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -65926,34 +65946,34 @@
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>938.587</v>
+        <v>3161</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1200</v>
+        <v>28000</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1.278517601458362</v>
+        <v>8.857956342929453</v>
       </c>
       <c r="H156" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.069950017100908</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.093266689467878</v>
+        <v>1.210185593879396</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-0.09326668946787797</v>
+        <v>-0.2101855938793955</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>-0.04260411680229781</v>
+        <v>0.07692307692307687</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>-0.3209678112733748</v>
+        <v>0</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>0.1257293774340067</v>
+        <v>0.04575379627485376</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>0</v>
@@ -65962,17 +65982,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AIR PRODUCTS AND CHEMICALS, INC.</t>
+          <t>Centrus Energy Corp.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -65981,34 +66001,34 @@
         </is>
       </c>
       <c r="E157" s="3" t="n">
-        <v>3161</v>
+        <v>176.1</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>28000</v>
+        <v>800</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>8.857956342929453</v>
+        <v>4.542873367404884</v>
       </c>
       <c r="H157" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>1.480891850388013</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>1.210185593879396</v>
+        <v>1.641189133850684</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-0.2101855938793955</v>
+        <v>-0.6411891338506841</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="M157" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>0.04575379627485376</v>
+        <v>0.1398058252427183</v>
       </c>
       <c r="O157" s="3" t="n">
         <v>0</v>
@@ -66017,53 +66037,53 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CTGG</t>
+          <t>COLD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>QWEST CORPORATION</t>
+          <t>AMERICOLD REALTY TRUST, INC.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Real Estate Investment Trusts</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>1051</v>
+        <v>662.89</v>
       </c>
       <c r="F158" s="3" t="n">
         <v>1700</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1.617507136060894</v>
+        <v>2.564528051411245</v>
       </c>
       <c r="H158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0.9137930393824609</v>
+        <v>1.119072189499421</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>0.8850573858432812</v>
+        <v>1.158762919332561</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0.1149426141567188</v>
+        <v>-0.1587629193325606</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>-0.1904761904761905</v>
+        <v>0.2142857142857142</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>0.03679653679653683</v>
+        <v>-0.09340659340659352</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>-0.1399345335515548</v>
+        <v>0.01865852833969517</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>0</v>
@@ -66072,17 +66092,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>RNG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>RingCentral, Inc.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Industrial Inorganic Chemicals</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -66091,34 +66111,34 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>9289</v>
+        <v>657.011</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>64000</v>
+        <v>2700</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>6.889869738400258</v>
+        <v>4.109520236343075</v>
       </c>
       <c r="H159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1.085960275519686</v>
+        <v>1.03880788389923</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>1.114613700692915</v>
+        <v>1.051743845198973</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-0.1146137006929147</v>
+        <v>-0.05174384519897313</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>0.04918032786885251</v>
+        <v>0.03846153846153855</v>
       </c>
       <c r="M159" s="5" t="n">
-        <v>-0.05426794799321644</v>
+        <v>0</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>0.09346674514420239</v>
+        <v>0.05901534176448009</v>
       </c>
       <c r="O159" s="3" t="n">
         <v>0</v>
@@ -66127,17 +66147,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DOCUSIGN, INC.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Inorganic Chemicals</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -66146,34 +66166,34 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>875.746</v>
+        <v>9289</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>2300</v>
+        <v>64000</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>2.626332292696741</v>
+        <v>6.889869738400258</v>
       </c>
       <c r="H160" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0.9997616187771211</v>
+        <v>1.085960275519686</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>0.9996821583694948</v>
+        <v>1.114613700692915</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0.000317841630505189</v>
+        <v>-0.1146137006929147</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>0</v>
+        <v>0.04918032786885251</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>0</v>
+        <v>-0.05426794799321644</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>0.09381291872960995</v>
+        <v>0.09346674514420239</v>
       </c>
       <c r="O160" s="3" t="n">
         <v>0</v>
@@ -66182,53 +66202,53 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>CTGG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TRIMBLE INC.</t>
+          <t>QWEST CORPORATION</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Measuring &amp; Controlling Devices, NEC</t>
+          <t>Telephone Communications (No Radiotelephone)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>972</v>
+        <v>1051</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>2.05761316872428</v>
+        <v>1.617507136060894</v>
       </c>
       <c r="H161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>1.077335533099608</v>
+        <v>0.9137930393824609</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>1.103114044132811</v>
+        <v>0.8850573858432812</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-0.1031140441328109</v>
+        <v>0.1149426141567188</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>0.1764705882352942</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>0</v>
+        <v>0.03679653679653683</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.1099691675231242</v>
+        <v>-0.1399345335515548</v>
       </c>
       <c r="O161" s="3" t="n">
         <v>0</v>
@@ -66237,17 +66257,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RYDER SYSTEM, INC.</t>
+          <t>Ciena Corp</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
+          <t>Telephone &amp; Telegraph Apparatus</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -66256,34 +66276,34 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>3347</v>
+        <v>1671.129</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>1.015835076187631</v>
+        <v>1.495994623993719</v>
       </c>
       <c r="H162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>1.015760444815641</v>
+        <v>1.089159548671955</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>1.021013926420854</v>
+        <v>1.171168102164085</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-0.02101392642085442</v>
+        <v>-0.1711681021640847</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>0.0625</v>
+        <v>0.25</v>
       </c>
       <c r="M162" s="5" t="n">
-        <v>0</v>
+        <v>-0.2205882352941178</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>0.04954531201003443</v>
+        <v>0.3704687198874841</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>0</v>
@@ -66292,17 +66312,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUMEN TECHNOLOGIES, INC.</t>
+          <t>Medpace Holdings, Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Telephone Communications (No Radiotelephone)</t>
+          <t>Services-Commercial Physical &amp; Biological Research</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -66311,34 +66331,34 @@
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>2805</v>
+        <v>707.331</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>5900</v>
+        <v>3500</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>2.103386809269162</v>
+        <v>4.948178434141866</v>
       </c>
       <c r="H163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>0.9914988391223929</v>
+        <v>0.9999078094493223</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>0.9886651188298572</v>
+        <v>0.9998770792657633</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0.01133488117014281</v>
+        <v>0.0001229207342366978</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>-0.01666666666666672</v>
+        <v>0</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>0.01612021857923496</v>
+        <v>-0.02941176470588225</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>-0.09282018111254853</v>
+        <v>0.1724152219999304</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>0</v>
@@ -66347,17 +66367,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp.</t>
+          <t>RYDER SYSTEM, INC.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
+          <t>Services-Auto Rental &amp; Leasing (No Drivers)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -66366,34 +66386,34 @@
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>176.1</v>
+        <v>3347</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>800</v>
+        <v>3400</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>4.542873367404884</v>
+        <v>1.015835076187631</v>
       </c>
       <c r="H164" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.480891850388013</v>
+        <v>1.015760444815641</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>1.641189133850684</v>
+        <v>1.021013926420854</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-0.6411891338506841</v>
+        <v>-0.02101392642085442</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0625</v>
       </c>
       <c r="M164" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0.1398058252427183</v>
+        <v>0.04954531201003443</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>0</v>
@@ -66402,17 +66422,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BlackLine, Inc.</t>
+          <t>TRIMBLE INC.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Measuring &amp; Controlling Devices, NEC</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -66421,34 +66441,34 @@
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>187.822</v>
+        <v>972</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>5.856608916953285</v>
+        <v>2.05761316872428</v>
       </c>
       <c r="H165" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>1.213236048111025</v>
+        <v>1.077335533099608</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>1.284314730814701</v>
+        <v>1.103114044132811</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-0.2843147308147007</v>
+        <v>-0.1031140441328109</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>0.1648840410886372</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>-0.03967136846020192</v>
+        <v>0</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>0.09182967591919766</v>
+        <v>0.1099691675231242</v>
       </c>
       <c r="O165" s="3" t="n">
         <v>0</v>
@@ -66457,12 +66477,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>BlackLine, Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -66476,34 +66496,34 @@
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>911.74</v>
+        <v>187.822</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1700</v>
+        <v>1100</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>1.864566652773817</v>
+        <v>5.856608916953285</v>
       </c>
       <c r="H166" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>1.118309234968699</v>
+        <v>1.213236048111025</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>1.157745646624932</v>
+        <v>1.284314730814701</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-0.1577456466249316</v>
+        <v>-0.2843147308147007</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.1648840410886372</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>-0.1887865655471288</v>
+        <v>-0.03967136846020192</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>0.1982924719990118</v>
+        <v>0.09182967591919766</v>
       </c>
       <c r="O166" s="3" t="n">
         <v>0</v>
@@ -66512,17 +66532,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>COLD</t>
+          <t>KNF</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AMERICOLD REALTY TRUST, INC.</t>
+          <t>Knife River Corporation</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Real Estate Investment Trusts</t>
+          <t>Mining &amp; Quarrying of  Nonmetallic Minerals (No Fuels)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -66531,34 +66551,34 @@
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>662.89</v>
+        <v>938.587</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>2.564528051411245</v>
+        <v>1.278517601458362</v>
       </c>
       <c r="H167" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1.119072189499421</v>
+        <v>1.069950017100908</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>1.158762919332561</v>
+        <v>1.093266689467878</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-0.1587629193325606</v>
+        <v>-0.09326668946787797</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>0.2142857142857142</v>
+        <v>-0.04260411680229781</v>
       </c>
       <c r="M167" s="5" t="n">
-        <v>-0.09340659340659352</v>
+        <v>-0.3209678112733748</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>0.01865852833969517</v>
+        <v>0.1257293774340067</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>0</v>
@@ -66622,17 +66642,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>RNG</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RingCentral, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -66641,34 +66661,34 @@
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>657.011</v>
+        <v>911.74</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2700</v>
+        <v>1700</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>4.109520236343075</v>
+        <v>1.864566652773817</v>
       </c>
       <c r="H169" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>1.03880788389923</v>
+        <v>1.118309234968699</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>1.051743845198973</v>
+        <v>1.157745646624932</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-0.05174384519897313</v>
+        <v>-0.1577456466249316</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>0.03846153846153855</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>0</v>
+        <v>-0.1887865655471288</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>0.05901534176448009</v>
+        <v>0.1982924719990118</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>0</v>
@@ -66677,17 +66697,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Medpace Holdings, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Services-Commercial Physical &amp; Biological Research</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -66696,53 +66716,53 @@
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>707.331</v>
+        <v>1121.454</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>3500</v>
+        <v>3471.4</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>4.948178434141866</v>
+        <v>3.095445733841959</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>1</v>
+        <v>0.9884079061646756</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0.9999078094493223</v>
+        <v>1.281662386208455</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>0.9998770792657633</v>
+        <v>1.379413879556381</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0.0001229207342366978</v>
+        <v>-0.3910059733917055</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>0</v>
+        <v>0.4310330612581417</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>-0.02941176470588225</v>
+        <v>-0.07801847620396307</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>0.1724152219999304</v>
+        <v>0.3564444336929702</v>
       </c>
       <c r="O170" s="3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Security &amp; Commodity Brokers, Dealers, Exchanges &amp; Services</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -66751,53 +66771,53 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>1121.454</v>
+        <v>2532</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>3471.4</v>
+        <v>3614</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>3.095445733841959</v>
+        <v>1.427330173775671</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>0.9884079061646756</v>
+        <v>0.9877567140600316</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>1.281662386208455</v>
+        <v>1.034368562333596</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>1.379413879556381</v>
+        <v>1.049905845091451</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-0.3910059733917055</v>
+        <v>-0.06214913103141906</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>0.4310330612581417</v>
+        <v>0.08822643781993378</v>
       </c>
       <c r="M171" s="5" t="n">
-        <v>-0.07801847620396307</v>
+        <v>-0.08041735826855612</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>0.3564444336929702</v>
+        <v>0.2051404093288911</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>-13</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>ALLIANCE RESOURCE PARTNERS LP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Security &amp; Commodity Brokers, Dealers, Exchanges &amp; Services</t>
+          <t>Bituminous Coal &amp; Lignite Surface Mining</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -66806,53 +66826,53 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>2532</v>
+        <v>551.5599999999999</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>3614</v>
+        <v>3635.759</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>1.427330173775671</v>
+        <v>6.591774240336501</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>0.9877567140600316</v>
+        <v>0.9868083254768296</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>1.034368562333596</v>
+        <v>1.001003515284542</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>1.049905845091451</v>
+        <v>1.005735245220445</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-0.06214913103141906</v>
+        <v>-0.01892691974361571</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>0.08822643781993378</v>
+        <v>0.00601045313039128</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.08041735826855612</v>
+        <v>-0.0905058310184037</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>0.2051404093288911</v>
+        <v>0.007483610764563053</v>
       </c>
       <c r="O172" s="3" t="n">
-        <v>-31</v>
+        <v>-7.27599999999984</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ALLIANCE RESOURCE PARTNERS LP</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bituminous Coal &amp; Lignite Surface Mining</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -66861,53 +66881,53 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>551.5599999999999</v>
+        <v>93.271</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>3635.759</v>
+        <v>151.039</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>6.591774240336501</v>
+        <v>1.619356498804559</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>0.9868083254768296</v>
+        <v>0.9848505966484759</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>1.001003515284542</v>
+        <v>0.9508476455958103</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>1.005735245220445</v>
+        <v>0.9395133285782548</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-0.01892691974361571</v>
+        <v>0.04533726807022109</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>0.00601045313039128</v>
+        <v>0.001352471243411646</v>
       </c>
       <c r="M173" s="5" t="n">
-        <v>-0.0905058310184037</v>
+        <v>-0.09380934047312151</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>0.007483610764563053</v>
+        <v>0.009907315171726827</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>-7.27599999999984</v>
+        <v>-1.413000000000011</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Industrial Trucks, Tractors, Trailors &amp; Stackers</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -66916,103 +66936,103 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>93.271</v>
+        <v>2238</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>151.039</v>
+        <v>3418</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>1.619356498804559</v>
+        <v>1.527256478999106</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>0.9848505966484759</v>
+        <v>0.9848078641644326</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>0.9508476455958103</v>
+        <v>1.489733157066897</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>0.9395133285782548</v>
+        <v>1.658041588034384</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0.04533726807022109</v>
+        <v>-0.6732337238699518</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>0.001352471243411646</v>
+        <v>109.258064516129</v>
       </c>
       <c r="M174" s="5" t="n">
-        <v>-0.09380934047312151</v>
+        <v>-4.808602150537624</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>0.009907315171726827</v>
+        <v>0.5050437121721587</v>
       </c>
       <c r="O174" s="3" t="n">
-        <v>-1.413000000000011</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>ADOBE INC.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Industrial Trucks, Tractors, Trailors &amp; Stackers</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q3</t>
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>2238</v>
+        <v>6760</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>3418</v>
+        <v>22160</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>1.527256478999106</v>
+        <v>3.27810650887574</v>
       </c>
       <c r="H175" s="4" t="n">
-        <v>0.9848078641644326</v>
+        <v>0.9837278106508875</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>1.489733157066897</v>
+        <v>1.070050539379989</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>1.658041588034384</v>
+        <v>1.098824782289689</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-0.6732337238699518</v>
+        <v>-0.1150969716388019</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>109.258064516129</v>
+        <v>0.08414872798434447</v>
       </c>
       <c r="M175" s="5" t="n">
-        <v>-4.808602150537624</v>
+        <v>-0.04688225220864695</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>0.5050437121721587</v>
+        <v>0.1289245156980627</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>-34</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ADOBE INC.</t>
+          <t>TERADATA CORPORATION</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -67022,162 +67042,162 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026Q3</t>
+          <t>2026Q2</t>
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>6760</v>
+        <v>410</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>22160</v>
+        <v>2026</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>3.27810650887574</v>
+        <v>4.941463414634146</v>
       </c>
       <c r="H176" s="4" t="n">
-        <v>0.9837278106508875</v>
+        <v>0.9829268292682927</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>1.070050539379989</v>
+        <v>1.114493530818356</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>1.098824782289689</v>
+        <v>1.158349098001711</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-0.1150969716388019</v>
+        <v>-0.1754222687334182</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>0.08414872798434447</v>
+        <v>0.1004888647474198</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>-0.04688225220864695</v>
+        <v>0.0732023564098756</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>0.1289245156980627</v>
+        <v>0.004901960784313708</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>-110</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TDC</t>
-        </is>
-      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TERADATA CORPORATION</t>
+          <t>BOARDWALK PIPELINE PARTNERS, LP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>Natural Gas Transmission</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>572.3</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>19568.5</v>
+      </c>
+      <c r="G177" s="4" t="n">
+        <v>34.19273108509523</v>
+      </c>
+      <c r="H177" s="4" t="n">
+        <v>0.9816529792067098</v>
+      </c>
+      <c r="I177" s="4" t="n">
+        <v>3.111446558642081</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>3.821377751787205</v>
+      </c>
+      <c r="K177" s="4" t="n">
+        <v>-2.839724772580495</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>0.3483893195521102</v>
+      </c>
+      <c r="M177" s="5" t="n">
+        <v>-0.03680294052076127</v>
+      </c>
+      <c r="N177" s="5" t="n">
+        <v>0.07172284644194749</v>
+      </c>
+      <c r="O177" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CRNC</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CERENCE INC.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>Services-Prepackaged Software</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>410</v>
-      </c>
-      <c r="F177" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G177" s="4" t="n">
-        <v>4.941463414634146</v>
-      </c>
-      <c r="H177" s="4" t="n">
-        <v>0.9829268292682927</v>
-      </c>
-      <c r="I177" s="4" t="n">
-        <v>1.114493530818356</v>
-      </c>
-      <c r="J177" s="4" t="n">
-        <v>1.158349098001711</v>
-      </c>
-      <c r="K177" s="4" t="n">
-        <v>-0.1754222687334182</v>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v>0.1004888647474198</v>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v>0.0732023564098756</v>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v>0.004901960784313708</v>
-      </c>
-      <c r="O177" s="3" t="n">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>BOARDWALK PIPELINE PARTNERS, LP</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Natural Gas Transmission</t>
-        </is>
-      </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>2026Q2</t>
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>572.3</v>
+        <v>69.587</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>19568.5</v>
+        <v>234.281</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>34.19273108509523</v>
+        <v>3.36673516605113</v>
       </c>
       <c r="H178" s="4" t="n">
-        <v>0.9816529792067098</v>
+        <v>0.980441749177289</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>3.111446558642081</v>
+        <v>1.038588013744781</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>3.821377751787205</v>
+        <v>1.153661965038793</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-2.839724772580495</v>
+        <v>-0.1732202158615037</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>0.3483893195521102</v>
+        <v>0.04346567374243948</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>-0.03680294052076127</v>
+        <v>-0.1102057353854111</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>0.07172284644194749</v>
+        <v>0.1181149174111449</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>-10.5</v>
+        <v>-1.36099999999999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CERENCE INC.</t>
+          <t>CONSTELLATION ENERGY CORPORATION</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Electric Services</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -67186,53 +67206,53 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>69.587</v>
+        <v>7504</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>234.281</v>
+        <v>11855</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>3.36673516605113</v>
+        <v>1.579824093816631</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>0.980441749177289</v>
+        <v>0.9761460554371002</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>1.038588013744781</v>
+        <v>1.248916952244267</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>1.153661965038793</v>
+        <v>1.339840584513322</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-0.1732202158615037</v>
+        <v>-0.3636945290762217</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>0.04346567374243948</v>
+        <v>12.86549707602339</v>
       </c>
       <c r="M179" s="5" t="n">
-        <v>-0.1102057353854111</v>
+        <v>-0.09505976852417142</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.1181149174111449</v>
+        <v>0.2299623012620882</v>
       </c>
       <c r="O179" s="3" t="n">
-        <v>-1.36099999999999</v>
+        <v>-179</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CONSTELLATION ENERGY CORPORATION</t>
+          <t>HEALTHSTREAM INC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Electric Services</t>
+          <t>Services-Computer Programming, Data Processing, Etc.</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -67241,53 +67261,53 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>7504</v>
+        <v>83.732</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>11855</v>
+        <v>685</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1.579824093816631</v>
+        <v>8.180862752591603</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>0.9761460554371002</v>
+        <v>0.9761142693354989</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>1.248916952244267</v>
+        <v>1.211069614193873</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>1.339840584513322</v>
+        <v>1.289388062479998</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-0.3636945290762217</v>
+        <v>-0.3132737931444993</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>12.86549707602339</v>
+        <v>0.1084142394822007</v>
       </c>
       <c r="M180" s="5" t="n">
-        <v>-0.09505976852417142</v>
+        <v>-0.01230354192073557</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>0.2299623012620882</v>
+        <v>0.1254906177751491</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>-179</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HEALTHSTREAM INC</t>
+          <t>Information Services Group Inc.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Services-Computer Programming, Data Processing, Etc.</t>
+          <t>Services-Management Consulting Services</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -67296,53 +67316,53 @@
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>83.732</v>
+        <v>65.488</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>685</v>
+        <v>121.4</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>8.180862752591603</v>
+        <v>1.853774737356462</v>
       </c>
       <c r="H181" s="4" t="n">
-        <v>0.9761142693354989</v>
+        <v>0.9755680430002444</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>1.211069614193873</v>
+        <v>1.038477210343448</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>1.289388062479998</v>
+        <v>1.059446932791182</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-0.3132737931444993</v>
+        <v>-0.08387888979093805</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>0.1084142394822007</v>
+        <v>0.08296164139161477</v>
       </c>
       <c r="M181" s="5" t="n">
-        <v>-0.01230354192073557</v>
+        <v>0.06221475342480987</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>0.1254906177751491</v>
+        <v>0.0637212702022254</v>
       </c>
       <c r="O181" s="3" t="n">
-        <v>-2</v>
+        <v>-1.599999999999994</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Information Services Group Inc.</t>
+          <t>OMNICELL, INC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Services-Management Consulting Services</t>
+          <t>Electronic Computers</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -67351,53 +67371,53 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>65.488</v>
+        <v>312.208</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>121.4</v>
+        <v>375.1</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>1.853774737356462</v>
+        <v>1.201442627991595</v>
       </c>
       <c r="H182" s="4" t="n">
-        <v>0.9755680430002444</v>
+        <v>0.9750166555629581</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>1.038477210343448</v>
+        <v>0.9927010897137809</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>1.059446932791182</v>
+        <v>0.9985959010973885</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-0.08387888979093805</v>
+        <v>-0.02357924553443036</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>0.08296164139161477</v>
+        <v>-0.02343139807341843</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>0.06221475342480987</v>
+        <v>-0.004220332499647927</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>0.0637212702022254</v>
+        <v>0.07449700924415459</v>
       </c>
       <c r="O182" s="3" t="n">
-        <v>-1.599999999999994</v>
+        <v>-7.799999999999955</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OMNICELL, INC</t>
+          <t>OTIS WORLDWIDE CORPORATION</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Electronic Computers</t>
+          <t>Electronic &amp; Other Electrical Equipment (No Computer Equip)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -67406,53 +67426,53 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>312.208</v>
+        <v>3859</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>375.1</v>
+        <v>19700</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>1.201442627991595</v>
+        <v>5.104949468774294</v>
       </c>
       <c r="H183" s="4" t="n">
-        <v>0.9750166555629581</v>
+        <v>0.9740865509199275</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>0.9927010897137809</v>
+        <v>1.028856907733441</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>0.9985959010973885</v>
+        <v>1.047113693337945</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-0.02357924553443036</v>
+        <v>-0.073027142418018</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>-0.02343139807341843</v>
+        <v>0.02072538860103634</v>
       </c>
       <c r="M183" s="5" t="n">
-        <v>-0.004220332499647927</v>
+        <v>-0.04379074043122166</v>
       </c>
       <c r="N183" s="5" t="n">
-        <v>0.07449700924415459</v>
+        <v>0.07343532684283738</v>
       </c>
       <c r="O183" s="3" t="n">
-        <v>-7.799999999999955</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OTIS WORLDWIDE CORPORATION</t>
+          <t>Honeywell International Inc</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Electronic &amp; Other Electrical Equipment (No Computer Equip)</t>
+          <t>Aircraft Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -67461,53 +67481,53 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>3859</v>
+        <v>9719</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>19700</v>
+        <v>38008</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>5.104949468774294</v>
+        <v>3.910690400246939</v>
       </c>
       <c r="H184" s="4" t="n">
-        <v>0.9740865509199275</v>
+        <v>0.9738656240353946</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>1.028856907733441</v>
+        <v>1.039543948203915</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>1.047113693337945</v>
+        <v>1.061436722926755</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-0.073027142418018</v>
+        <v>-0.08757109889135994</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>0.02072538860103634</v>
+        <v>0.03844157263462744</v>
       </c>
       <c r="M184" s="5" t="n">
-        <v>-0.04379074043122166</v>
+        <v>-0.02153571079612848</v>
       </c>
       <c r="N184" s="5" t="n">
-        <v>0.07343532684283738</v>
+        <v>0.04258742759064571</v>
       </c>
       <c r="O184" s="3" t="n">
-        <v>-100</v>
+        <v>-254</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Honeywell International Inc</t>
+          <t>ENTERPRISE PRODUCTS PARTNERS L.P.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Aircraft Engines &amp; Engine Parts</t>
+          <t>Natural Gas Transmission</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -67516,53 +67536,53 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>9719</v>
+        <v>18269</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>38008</v>
+        <v>25935</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>3.910690400246939</v>
+        <v>1.419617932015983</v>
       </c>
       <c r="H185" s="4" t="n">
-        <v>0.9738656240353946</v>
+        <v>0.9736712463736384</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>1.039543948203915</v>
+        <v>0.9731546633796452</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>1.061436722926755</v>
+        <v>0.9729824690483141</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-0.08757109889135994</v>
+        <v>0.0006887773253243523</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>0.03844157263462744</v>
+        <v>-0.05660034193008623</v>
       </c>
       <c r="M185" s="5" t="n">
-        <v>-0.02153571079612848</v>
+        <v>-0.08318203010045777</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>0.04258742759064571</v>
+        <v>0.6077620346739416</v>
       </c>
       <c r="O185" s="3" t="n">
-        <v>-254</v>
+        <v>-481</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ENTERPRISE PRODUCTS PARTNERS L.P.</t>
+          <t>DXC TECHNOLOGY COMPANY</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Natural Gas Transmission</t>
+          <t>Services-Computer Processing &amp; Data Preparation</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -67571,53 +67591,53 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>18269</v>
+        <v>2999</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>25935</v>
+        <v>16300</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>1.419617932015983</v>
+        <v>5.43514504834945</v>
       </c>
       <c r="H186" s="4" t="n">
-        <v>0.9736712463736384</v>
+        <v>0.9666555518506169</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.9731546633796452</v>
+        <v>0.9571406740666194</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>0.9729824690483141</v>
+        <v>0.9471517653089853</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0.0006887773253243523</v>
+        <v>0.01950378654163165</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>-0.05660034193008623</v>
+        <v>-0.0239520958083832</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>-0.08318203010045777</v>
+        <v>0.005633703008184887</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>0.6077620346739416</v>
+        <v>-0.05064893953782845</v>
       </c>
       <c r="O186" s="3" t="n">
-        <v>-481</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DXC TECHNOLOGY COMPANY</t>
+          <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Services-Computer Processing &amp; Data Preparation</t>
+          <t>Services-Prepackaged Software</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -67626,48 +67646,48 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>2999</v>
+        <v>310.4</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>16300</v>
+        <v>1172</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>5.43514504834945</v>
+        <v>3.775773195876289</v>
       </c>
       <c r="H187" s="4" t="n">
-        <v>0.9666555518506169</v>
+        <v>0.9632731958762883</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>0.9571406740666194</v>
+        <v>1.014768836974761</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>0.9471517653089853</v>
+        <v>1.031934050674251</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0.01950378654163165</v>
+        <v>-0.0686608547979628</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>-0.0239520958083832</v>
+        <v>0.01833347814753661</v>
       </c>
       <c r="M187" s="5" t="n">
-        <v>0.005633703008184887</v>
+        <v>-0.02975792208273553</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>-0.05064893953782845</v>
+        <v>0.01206390609716324</v>
       </c>
       <c r="O187" s="3" t="n">
-        <v>-100</v>
+        <v>-11.40000000000009</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZoomInfo Technologies Inc.</t>
+          <t>SYNOPSYS INC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -67681,53 +67701,53 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>310.4</v>
+        <v>2476.822</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>1172</v>
+        <v>10900</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>3.775773195876289</v>
+        <v>4.400800703482123</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>0.9632731958762883</v>
+        <v>0.9596256816194301</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>1.014768836974761</v>
+        <v>0.9287667126997182</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>1.031934050674251</v>
+        <v>1.325424501690517</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>-0.0686608547979628</v>
+        <v>-0.3657988200710872</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>0.01833347814753661</v>
+        <v>0.07920792079207928</v>
       </c>
       <c r="M188" s="5" t="n">
-        <v>-0.02975792208273553</v>
+        <v>-0.2788167705659454</v>
       </c>
       <c r="N188" s="5" t="n">
-        <v>0.01206390609716324</v>
+        <v>0.4236761073656536</v>
       </c>
       <c r="O188" s="3" t="n">
-        <v>-11.40000000000009</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SYNOPSYS INC</t>
+          <t>LOEWS CORP</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Services-Prepackaged Software</t>
+          <t>Fire, Marine &amp; Casualty Insurance</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -67736,53 +67756,53 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>2476.822</v>
+        <v>4734</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>10900</v>
+        <v>23500</v>
       </c>
       <c r="G189" s="4" t="n">
-        <v>4.400800703482123</v>
+        <v>4.964089564850021</v>
       </c>
       <c r="H189" s="4" t="n">
-        <v>0.9596256816194301</v>
+        <v>0.957752429235319</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>0.9287667126997182</v>
+        <v>1.238419926503082</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>1.325424501690517</v>
+        <v>1.33197575892567</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>-0.3657988200710872</v>
+        <v>-0.3742233296903508</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>0.07920792079207928</v>
+        <v>0.236842105263158</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>-0.2788167705659454</v>
+        <v>-0.03053757388122702</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>0.4236761073656536</v>
+        <v>0.039297475301866</v>
       </c>
       <c r="O189" s="3" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XPOF</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LOEWS CORP</t>
+          <t>Xponential Fitness, Inc.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Fire, Marine &amp; Casualty Insurance</t>
+          <t>Services-Miscellaneous Amusement &amp; Recreation</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -67791,92 +67811,92 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>4734</v>
+        <v>65.968</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>23500</v>
+        <v>74.839</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>4.964089564850021</v>
+        <v>1.134474290565122</v>
       </c>
       <c r="H190" s="4" t="n">
-        <v>0.957752429235319</v>
+        <v>0.9566911229687122</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>1.238419926503082</v>
+        <v>0.8828957593013692</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>1.33197575892567</v>
+        <v>0.8582973047455882</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-0.3742233296903508</v>
+        <v>0.09839381822312399</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>0.236842105263158</v>
+        <v>-0.3282017217080636</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>-0.03053757388122702</v>
+        <v>-0.01221161703243479</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>0.039297475301866</v>
+        <v>-0.1343690951081251</v>
       </c>
       <c r="O190" s="3" t="n">
-        <v>-200</v>
+        <v>-2.856999999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>XPOF</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Xponential Fitness, Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Services-Miscellaneous Amusement &amp; Recreation</t>
+          <t>Services-Business Services, NEC</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026Q2</t>
+          <t>2026Q3</t>
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>65.968</v>
+        <v>18679.11</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>74.839</v>
+        <v>37000</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>1.134474290565122</v>
+        <v>1.980822426764444</v>
       </c>
       <c r="H191" s="4" t="n">
-        <v>0.9566911229687122</v>
+        <v>0.9464642587360961</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>0.8828957593013692</v>
+        <v>1.04102096617605</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>0.8582973047455882</v>
+        <v>1.072539868656035</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0.09839381822312399</v>
+        <v>-0.1260756099199387</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>-0.3282017217080636</v>
+        <v>0.08823529411764697</v>
       </c>
       <c r="M191" s="5" t="n">
-        <v>-0.01221161703243479</v>
+        <v>-0.06327985739750464</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>-0.1343690951081251</v>
+        <v>0.0615386451439115</v>
       </c>
       <c r="O191" s="3" t="n">
-        <v>-2.856999999999999</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="192">
